--- a/youzi/北京帮/index.xlsx
+++ b/youzi/北京帮/index.xlsx
@@ -39,6 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
@@ -51,19 +93,3259 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E6CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4654"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,37 +3357,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,67 +3489,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,439 +3525,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -633,667 +3555,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1311,1249 +3621,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E6CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2565,1056 +3645,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA91E2B"/>
         <bgColor/>
       </patternFill>
@@ -3639,49 +3669,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -10314,7 +10314,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -3320.73万</v>
       </c>
       <c r="E2">
@@ -10329,40 +10329,40 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
       <c r="J2" s="5">
         <v>2.04</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="3">
         <v>4.88</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="8">
         <v>7.07</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="13">
         <v>7.94</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>10.06</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="10">
         <v>21.06</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="11">
         <v>33.16</v>
       </c>
       <c r="Q2" s="12">
         <v>23.03</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="6">
         <v>25.8</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="4">
         <v>24.05</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="1">
         <v>-32</v>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       <c r="C3" t="str">
         <v>000710</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="20" t="str">
         <v>净卖: -1108.14万</v>
       </c>
       <c r="E3">
@@ -10391,40 +10391,40 @@
       <c r="H3">
         <v>-0.08</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="21">
         <v>10.1</v>
       </c>
       <c r="J3" s="14">
         <v>21.13</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="17">
         <v>18.96</v>
       </c>
       <c r="L3" s="22">
         <v>30.85</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="18">
         <v>34.5</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="25">
         <v>40.64</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="23">
         <v>46.7</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="19">
         <v>42.19</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="15">
         <v>33.49</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="26">
         <v>34.19</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="16">
         <v>25.8</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="24">
         <v>-21.83</v>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       <c r="C4" t="str">
         <v>601616</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="36" t="str">
         <v>净卖: -513.00万</v>
       </c>
       <c r="E4">
@@ -10453,40 +10453,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="34">
         <v>9.62</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="37">
         <v>6.41</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="38">
         <v>7.26</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="27">
         <v>5.34</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="28">
         <v>7.69</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="29">
         <v>7.91</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="32">
         <v>7.69</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="30">
         <v>3.85</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="33">
         <v>0.43</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="39">
         <v>2.35</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="35">
         <v>4.27</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="31">
         <v>2.78</v>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       <c r="C5" t="str">
         <v>600370</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="47" t="str">
         <v>净卖: -194.00万</v>
       </c>
       <c r="E5">
@@ -10515,40 +10515,40 @@
       <c r="H5">
         <v>-1.14</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="52">
         <v>11.49</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="40">
         <v>22.41</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="41">
         <v>16.09</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="42">
         <v>27.59</v>
       </c>
       <c r="M5" s="48">
         <v>25.29</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="50">
         <v>20.11</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="49">
         <v>14.37</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="43">
         <v>2.87</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="44">
         <v>-5.75</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="51">
         <v>-5.75</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="45">
         <v>-3.45</v>
       </c>
-      <c r="T5" s="43">
+      <c r="T5" s="46">
         <v>37.93</v>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       <c r="C6" t="str">
         <v>603123</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="65" t="str">
         <v>净卖: -3403.34万</v>
       </c>
       <c r="E6">
@@ -10577,40 +10577,40 @@
       <c r="H6">
         <v>-6.28</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="56">
         <v>17.38</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="57">
         <v>8.2</v>
       </c>
       <c r="K6" s="53">
         <v>5.96</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="58">
         <v>0.41</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="59">
         <v>3.31</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="63">
         <v>-2.15</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="54">
         <v>-7.95</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="60">
         <v>-2.15</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="55">
         <v>-0.66</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="64">
         <v>9.27</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="61">
         <v>2.57</v>
       </c>
-      <c r="T6" s="59">
+      <c r="T6" s="62">
         <v>2.73</v>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       <c r="C7" t="str">
         <v>603616</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="75" t="str">
         <v>净卖: -196.32万</v>
       </c>
       <c r="E7">
@@ -10645,34 +10645,34 @@
       <c r="J7" s="69">
         <v>8.4</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="70">
         <v>12.35</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="66">
         <v>14.07</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="71">
         <v>12.84</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="76">
         <v>24.2</v>
       </c>
-      <c r="O7" s="76">
+      <c r="O7" s="77">
         <v>18.27</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="78">
         <v>13.58</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="72">
         <v>12.35</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="67">
         <v>14.07</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="73">
         <v>10.86</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="74">
         <v>57.28</v>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       <c r="C8" t="str">
         <v>600399</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="81" t="str">
         <v>净卖: -1684.57万</v>
       </c>
       <c r="E8">
@@ -10701,40 +10701,40 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="88">
         <v>10.06</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="86">
         <v>5.69</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="82">
         <v>4.93</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="79">
         <v>7.59</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="83">
         <v>5.69</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="80">
         <v>5.88</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="89">
         <v>10.44</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="90">
         <v>13.47</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="87">
         <v>11.01</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="91">
         <v>13.47</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="84">
         <v>13.28</v>
       </c>
-      <c r="T8" s="82">
+      <c r="T8" s="85">
         <v>12.14</v>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       <c r="C9" t="str">
         <v>605099</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="96" t="str">
         <v>净买: 320.21万</v>
       </c>
       <c r="E9">
@@ -10763,40 +10763,40 @@
       <c r="H9">
         <v>-9.03</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="92">
         <v>-1.06</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="93">
         <v>-9.31</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="97">
         <v>-12.01</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="103">
         <v>-13.02</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="98">
         <v>-12.9</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="100">
         <v>-14.41</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="101">
         <v>-14.02</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="102">
         <v>-14.24</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="99">
         <v>-12.96</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="94">
         <v>-11.51</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="104">
         <v>-12.1</v>
       </c>
-      <c r="T9" s="93">
+      <c r="T9" s="95">
         <v>12.07</v>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       <c r="C10" t="str">
         <v>600581</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="112" t="str">
         <v>净卖: -685.48万</v>
       </c>
       <c r="E10">
@@ -10825,13 +10825,13 @@
       <c r="H10">
         <v>-0.26</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="107">
         <v>10.42</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="113">
         <v>21.35</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="117">
         <v>33.59</v>
       </c>
       <c r="L10" s="109">
@@ -10846,19 +10846,19 @@
       <c r="O10" s="115">
         <v>16.41</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="108">
         <v>16.15</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="105">
         <v>19.79</v>
       </c>
       <c r="R10" s="106">
         <v>17.19</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="111">
         <v>17.97</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="116">
         <v>-21.09</v>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       <c r="C11" t="str">
         <v>836504</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="123" t="str">
         <v>净卖: -1178.54万</v>
       </c>
       <c r="E11">
@@ -10887,40 +10887,40 @@
       <c r="H11">
         <v>1.46</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="130">
         <v>16.5</v>
       </c>
-      <c r="J11" s="129">
+      <c r="J11" s="124">
         <v>6.23</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="128">
         <v>6.44</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="118">
         <v>3.7</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="129">
         <v>4.21</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="121">
         <v>1.81</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="125">
         <v>-0.75</v>
       </c>
-      <c r="P11" s="118">
+      <c r="P11" s="126">
         <v>0.24</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="119">
         <v>0.48</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="120">
         <v>2.02</v>
       </c>
       <c r="S11" s="127">
         <v>2.84</v>
       </c>
-      <c r="T11" s="128">
+      <c r="T11" s="122">
         <v>-5.07</v>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       <c r="C12" t="str">
         <v>836504</v>
       </c>
-      <c r="D12" s="137" t="str">
+      <c r="D12" s="132" t="str">
         <v>净买: 584.91万</v>
       </c>
       <c r="E12">
@@ -10949,40 +10949,40 @@
       <c r="H12">
         <v>-5.97</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="133">
         <v>-3.03</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="138">
         <v>-2.84</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="134">
         <v>-5.34</v>
       </c>
       <c r="L12" s="139">
         <v>-4.87</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="140">
         <v>-7.06</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="135">
         <v>-9.41</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="136">
         <v>-8.5</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="131">
         <v>-8.28</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="137">
         <v>-6.87</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="141">
         <v>-6.13</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="142">
         <v>-10.38</v>
       </c>
-      <c r="T12" s="136">
+      <c r="T12" s="143">
         <v>-13.34</v>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       <c r="C13" t="str">
         <v>873679</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="144" t="str">
         <v>净卖: -359.87万</v>
       </c>
       <c r="E13">
@@ -11011,40 +11011,40 @@
       <c r="H13">
         <v>1.77</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="149">
         <v>7.59</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="156">
         <v>7.75</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="152">
         <v>1.45</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="145">
         <v>-3.03</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="146">
         <v>-6.09</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="147">
         <v>-4.27</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="148">
         <v>-0.5</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="150">
         <v>1.08</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="153">
         <v>4.19</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="154">
         <v>-2.78</v>
       </c>
       <c r="S13" s="151">
         <v>4.44</v>
       </c>
-      <c r="T13" s="147">
+      <c r="T13" s="155">
         <v>-5.64</v>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       <c r="C14" t="str">
         <v>002378</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -5673.94万</v>
       </c>
       <c r="E14">
@@ -11073,40 +11073,40 @@
       <c r="H14">
         <v>6.91</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="158">
         <v>2.92</v>
       </c>
-      <c r="J14" s="161">
+      <c r="J14" s="157">
         <v>12.54</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="159">
         <v>18.46</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="160">
         <v>15</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="161">
         <v>14.23</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="168">
         <v>19.31</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="162">
         <v>22.23</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="169">
         <v>11.46</v>
       </c>
-      <c r="Q14" s="162">
+      <c r="Q14" s="163">
         <v>2.38</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="164">
         <v>6.15</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="165">
         <v>7.92</v>
       </c>
-      <c r="T14" s="168">
+      <c r="T14" s="166">
         <v>150.38</v>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
       <c r="C15" t="str">
         <v>688228</v>
       </c>
-      <c r="D15" s="177" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -2485.38万</v>
       </c>
       <c r="E15">
@@ -11138,37 +11138,37 @@
       <c r="I15" s="170">
         <v>3.13</v>
       </c>
-      <c r="J15" s="178">
+      <c r="J15" s="174">
         <v>20.16</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="178">
         <v>13.29</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="171">
         <v>1.3</v>
       </c>
-      <c r="M15" s="180">
+      <c r="M15" s="175">
         <v>1.88</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="176">
         <v>-10.94</v>
       </c>
-      <c r="O15" s="181">
+      <c r="O15" s="172">
         <v>-8.2</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="177">
         <v>-3.3</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="179">
         <v>-0.78</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="181">
         <v>4.05</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="180">
         <v>10.16</v>
       </c>
-      <c r="T15" s="176">
+      <c r="T15" s="182">
         <v>-14.13</v>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       <c r="C16" t="str">
         <v>688228</v>
       </c>
-      <c r="D16" s="193" t="str">
+      <c r="D16" s="185" t="str">
         <v>净卖: -1919.36万</v>
       </c>
       <c r="E16">
@@ -11197,34 +11197,34 @@
       <c r="H16">
         <v>-1.95</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="189">
         <v>18.84</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="186">
         <v>12.05</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="193">
         <v>0.19</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="194">
         <v>0.76</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="195">
         <v>-11.91</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="187">
         <v>-9.21</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="190">
         <v>-4.37</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="184">
         <v>-1.87</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="188">
         <v>2.91</v>
       </c>
-      <c r="R16" s="188">
+      <c r="R16" s="183">
         <v>8.95</v>
       </c>
       <c r="S16" s="191">
@@ -11259,28 +11259,28 @@
       <c r="H17">
         <v>-0.89</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="202">
         <v>18.47</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="208">
         <v>27.43</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="203">
         <v>16.82</v>
       </c>
-      <c r="L17" s="202">
+      <c r="L17" s="196">
         <v>16.4</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="204">
         <v>51.27</v>
       </c>
-      <c r="N17" s="196">
+      <c r="N17" s="197">
         <v>37.28</v>
       </c>
-      <c r="O17" s="204">
+      <c r="O17" s="207">
         <v>26.95</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="205">
         <v>22.67</v>
       </c>
       <c r="Q17" s="198">
@@ -11289,10 +11289,10 @@
       <c r="R17" s="199">
         <v>36.39</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="206">
         <v>33.01</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="200">
         <v>11.65</v>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       <c r="C18" t="str">
         <v>836422</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="216" t="str">
         <v>净卖: -1044.29万</v>
       </c>
       <c r="E18">
@@ -11321,37 +11321,37 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="217">
         <v>29.97</v>
       </c>
-      <c r="J18" s="215">
+      <c r="J18" s="218">
         <v>33.59</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="210">
         <v>15.79</v>
       </c>
-      <c r="L18" s="217">
+      <c r="L18" s="211">
         <v>11.13</v>
       </c>
-      <c r="M18" s="210">
+      <c r="M18" s="212">
         <v>11.61</v>
       </c>
-      <c r="N18" s="220">
+      <c r="N18" s="219">
         <v>9.25</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="220">
         <v>11.27</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="213">
         <v>9.74</v>
       </c>
       <c r="Q18" s="221">
         <v>5.84</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="214">
         <v>8.55</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="215">
         <v>10.78</v>
       </c>
       <c r="T18" s="209">
@@ -11368,7 +11368,7 @@
       <c r="C19" t="str">
         <v>600157</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="230" t="str">
         <v>净卖: -4374.77万</v>
       </c>
       <c r="E19">
@@ -11383,40 +11383,40 @@
       <c r="H19">
         <v>1.94</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="223">
         <v>8.23</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="224">
         <v>6.96</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="234">
         <v>2.53</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="231">
         <v>8.86</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="222">
         <v>5.06</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="232">
         <v>1.9</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="225">
         <v>1.9</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="228">
         <v>2.53</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="229">
         <v>3.16</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="226">
         <v>7.59</v>
       </c>
       <c r="S19" s="233">
         <v>8.86</v>
       </c>
-      <c r="T19" s="234">
+      <c r="T19" s="227">
         <v>6.33</v>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       <c r="C20" t="str">
         <v>838030</v>
       </c>
-      <c r="D20" s="236" t="str">
+      <c r="D20" s="240" t="str">
         <v>净卖: -909.25万</v>
       </c>
       <c r="E20">
@@ -11445,36 +11445,36 @@
       <c r="H20">
         <v>0.13</v>
       </c>
-      <c r="I20" s="242">
+      <c r="I20" s="235">
         <v>29.83</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="241">
         <v>13.53</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="236">
         <v>7.1</v>
       </c>
-      <c r="L20" s="245">
+      <c r="L20" s="244">
         <v>4.99</v>
       </c>
-      <c r="M20" s="243">
+      <c r="M20" s="242">
         <v>4.73</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="245">
         <v>0.92</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="243">
         <v>0.79</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="237">
         <v>0.53</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="238">
         <v>-0.92</v>
       </c>
       <c r="R20" t="str"/>
       <c r="S20" t="str"/>
-      <c r="T20" s="240">
+      <c r="T20" s="239">
         <v>-0.92</v>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       <c r="C21" t="str">
         <v>600172</v>
       </c>
-      <c r="D21" s="257" t="str">
+      <c r="D21" s="256" t="str">
         <v>净卖: -1385.56万</v>
       </c>
       <c r="E21">
@@ -11503,40 +11503,40 @@
       <c r="H21">
         <v>-1.26</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="251">
         <v>11.49</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="252">
         <v>9.15</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="258">
         <v>8.72</v>
       </c>
-      <c r="L21" s="247">
+      <c r="L21" s="246">
         <v>7.66</v>
       </c>
-      <c r="M21" s="250">
+      <c r="M21" s="247">
         <v>7.87</v>
       </c>
-      <c r="N21" s="246">
+      <c r="N21" s="253">
         <v>10.85</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="248">
         <v>17.66</v>
       </c>
-      <c r="P21" s="252">
+      <c r="P21" s="249">
         <v>17.45</v>
       </c>
       <c r="Q21" s="255">
         <v>29.15</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="254">
         <v>30.85</v>
       </c>
-      <c r="S21" s="256">
+      <c r="S21" s="250">
         <v>36.6</v>
       </c>
-      <c r="T21" s="253">
+      <c r="T21" s="257">
         <v>86.6</v>
       </c>
     </row>
@@ -11568,37 +11568,37 @@
       <c r="I22" s="259">
         <v>10.11</v>
       </c>
-      <c r="J22" s="260">
+      <c r="J22" s="265">
         <v>3.83</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="260">
         <v>3.12</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="261">
         <v>4.02</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="266">
         <v>10.11</v>
       </c>
       <c r="N22" s="269">
         <v>6.05</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="262">
         <v>5.75</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="267">
         <v>13.23</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="270">
         <v>19.02</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="263">
         <v>14.17</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="268">
         <v>11.5</v>
       </c>
-      <c r="T22" s="267">
+      <c r="T22" s="264">
         <v>33.35</v>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       <c r="C23" t="str">
         <v>601212</v>
       </c>
-      <c r="D23" s="272" t="str">
+      <c r="D23" s="276" t="str">
         <v>净卖: -4295.10万</v>
       </c>
       <c r="E23">
@@ -11627,28 +11627,28 @@
       <c r="H23">
         <v>-0.39</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="277">
         <v>10.47</v>
       </c>
-      <c r="J23" s="283">
+      <c r="J23" s="282">
         <v>9.29</v>
       </c>
-      <c r="K23" s="273">
+      <c r="K23" s="283">
         <v>6.72</v>
       </c>
-      <c r="L23" s="274">
+      <c r="L23" s="273">
         <v>17.39</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="284">
         <v>29.05</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="274">
         <v>16.21</v>
       </c>
-      <c r="O23" s="276">
+      <c r="O23" s="281">
         <v>11.46</v>
       </c>
-      <c r="P23" s="277">
+      <c r="P23" s="278">
         <v>6.32</v>
       </c>
       <c r="Q23" s="279">
@@ -11657,10 +11657,10 @@
       <c r="R23" s="280">
         <v>2.77</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="272">
         <v>4.74</v>
       </c>
-      <c r="T23" s="281">
+      <c r="T23" s="275">
         <v>59.29</v>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       <c r="C24" t="str">
         <v>600740</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="290" t="str">
         <v>净买: 1621.89万</v>
       </c>
       <c r="E24">
@@ -11689,40 +11689,40 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="285">
+      <c r="I24" s="286">
         <v>10.07</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="291">
         <v>1.92</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="288">
         <v>2.88</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="292">
         <v>4.32</v>
       </c>
-      <c r="M24" s="286">
+      <c r="M24" s="296">
         <v>6.71</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="287">
         <v>2.88</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="297">
         <v>2.4</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="289">
         <v>4.08</v>
       </c>
-      <c r="Q24" s="291">
+      <c r="Q24" s="293">
         <v>3.36</v>
       </c>
-      <c r="R24" s="288">
+      <c r="R24" s="294">
         <v>5.28</v>
       </c>
-      <c r="S24" s="289">
+      <c r="S24" s="295">
         <v>6.95</v>
       </c>
-      <c r="T24" s="297">
+      <c r="T24" s="285">
         <v>-0.48</v>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       <c r="C25" t="str">
         <v>603122</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="299" t="str">
         <v>净卖: -503.06万</v>
       </c>
       <c r="E25">
@@ -11751,37 +11751,37 @@
       <c r="H25">
         <v>7.07</v>
       </c>
-      <c r="I25" s="298">
+      <c r="I25" s="310">
         <v>2.8</v>
       </c>
-      <c r="J25" s="299">
+      <c r="J25" s="304">
         <v>13.09</v>
       </c>
-      <c r="K25" s="307">
+      <c r="K25" s="305">
         <v>24.4</v>
       </c>
-      <c r="L25" s="301">
+      <c r="L25" s="298">
         <v>36.85</v>
       </c>
       <c r="M25" s="300">
         <v>50.57</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="306">
         <v>65.69</v>
       </c>
-      <c r="O25" s="303">
+      <c r="O25" s="307">
         <v>82.21</v>
       </c>
-      <c r="P25" s="308">
+      <c r="P25" s="301">
         <v>100.38</v>
       </c>
-      <c r="Q25" s="310">
+      <c r="Q25" s="302">
         <v>110.93</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="303">
         <v>132.02</v>
       </c>
-      <c r="S25" s="305">
+      <c r="S25" s="308">
         <v>155.27</v>
       </c>
       <c r="T25" s="309">
@@ -11798,7 +11798,7 @@
       <c r="C26" t="str">
         <v>002748</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="322" t="str">
         <v>净卖: -3194.79万</v>
       </c>
       <c r="E26">
@@ -11813,40 +11813,40 @@
       <c r="H26">
         <v>-2.87</v>
       </c>
-      <c r="I26" s="312">
+      <c r="I26" s="319">
         <v>-7.31</v>
       </c>
-      <c r="J26" s="313">
+      <c r="J26" s="318">
         <v>-11.37</v>
       </c>
-      <c r="K26" s="320">
+      <c r="K26" s="323">
         <v>-8.41</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="311">
         <v>-9.37</v>
       </c>
-      <c r="M26" s="318">
+      <c r="M26" s="312">
         <v>-6.42</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="313">
         <v>-9.67</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="314">
         <v>-7.38</v>
       </c>
-      <c r="P26" s="323">
+      <c r="P26" s="315">
         <v>-6.64</v>
       </c>
-      <c r="Q26" s="311">
+      <c r="Q26" s="316">
         <v>-2.88</v>
       </c>
-      <c r="R26" s="314">
+      <c r="R26" s="320">
         <v>-1.4</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="321">
         <v>5.61</v>
       </c>
-      <c r="T26" s="315">
+      <c r="T26" s="317">
         <v>-9.37</v>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       <c r="C27" t="str">
         <v>002591</v>
       </c>
-      <c r="D27" s="333" t="str">
+      <c r="D27" s="336" t="str">
         <v>净买: 2640.64万</v>
       </c>
       <c r="E27">
@@ -11875,40 +11875,40 @@
       <c r="H27">
         <v>1.86</v>
       </c>
-      <c r="I27" s="334">
+      <c r="I27" s="324">
         <v>3.65</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="334">
         <v>3.04</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="325">
         <v>13.37</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="326">
         <v>24.77</v>
       </c>
-      <c r="M27" s="329">
+      <c r="M27" s="332">
         <v>12.31</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="327">
         <v>10.49</v>
       </c>
-      <c r="O27" s="324">
+      <c r="O27" s="333">
         <v>7.6</v>
       </c>
-      <c r="P27" s="325">
+      <c r="P27" s="330">
         <v>3.8</v>
       </c>
       <c r="Q27" s="331">
         <v>6.23</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="328">
         <v>10.33</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="329">
         <v>15.35</v>
       </c>
-      <c r="T27" s="332">
+      <c r="T27" s="335">
         <v>4.26</v>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       <c r="C28" t="str">
         <v>002591</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="341" t="str">
         <v>净卖: -2864.29万</v>
       </c>
       <c r="E28">
@@ -11937,40 +11937,40 @@
       <c r="H28">
         <v>10.05</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="347">
         <v>0</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="348">
         <v>-9.99</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="349">
         <v>-11.45</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="339">
         <v>-13.76</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="340">
         <v>-16.81</v>
       </c>
-      <c r="N28" s="348">
+      <c r="N28" s="342">
         <v>-14.86</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="343">
         <v>-11.57</v>
       </c>
-      <c r="P28" s="338">
+      <c r="P28" s="344">
         <v>-7.55</v>
       </c>
       <c r="Q28" s="337">
         <v>-10.6</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="338">
         <v>-12.79</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="345">
         <v>-12.18</v>
       </c>
-      <c r="T28" s="339">
+      <c r="T28" s="346">
         <v>-16.44</v>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       <c r="C29" t="str">
         <v>920834</v>
       </c>
-      <c r="D29" s="358" t="str">
+      <c r="D29" s="353" t="str">
         <v>净买: 444.90万</v>
       </c>
       <c r="E29">
@@ -11999,40 +11999,40 @@
       <c r="H29">
         <v>0.05</v>
       </c>
-      <c r="I29" s="354">
+      <c r="I29" s="362">
         <v>4.65</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="354">
         <v>8.98</v>
       </c>
-      <c r="K29" s="360">
+      <c r="K29" s="351">
         <v>-2.49</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="355">
         <v>-6.06</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="360">
         <v>-1.24</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="361">
         <v>-3.08</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="352">
         <v>-8.49</v>
       </c>
-      <c r="P29" s="350">
+      <c r="P29" s="356">
         <v>-8.22</v>
       </c>
-      <c r="Q29" s="351">
+      <c r="Q29" s="350">
         <v>-9.84</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="357">
         <v>-1.03</v>
       </c>
-      <c r="S29" s="357">
+      <c r="S29" s="358">
         <v>-3.62</v>
       </c>
-      <c r="T29" s="355">
+      <c r="T29" s="359">
         <v>-33.8</v>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
       <c r="C30" t="str">
         <v>000592</v>
       </c>
-      <c r="D30" s="363" t="str">
+      <c r="D30" s="364" t="str">
         <v>净卖: -3288.03万</v>
       </c>
       <c r="E30">
@@ -12061,40 +12061,40 @@
       <c r="H30">
         <v>0.91</v>
       </c>
-      <c r="I30" s="364">
+      <c r="I30" s="374">
         <v>9.02</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="365">
         <v>19.94</v>
       </c>
-      <c r="K30" s="369">
+      <c r="K30" s="366">
         <v>7.92</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="375">
         <v>-2.91</v>
       </c>
       <c r="M30" s="370">
         <v>-0.5</v>
       </c>
-      <c r="N30" s="374">
+      <c r="N30" s="371">
         <v>-6.41</v>
       </c>
-      <c r="O30" s="371">
+      <c r="O30" s="372">
         <v>-2.3</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="367">
         <v>7.52</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="363">
         <v>13.93</v>
       </c>
-      <c r="R30" s="372">
+      <c r="R30" s="368">
         <v>25.35</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="373">
         <v>12.93</v>
       </c>
-      <c r="T30" s="375">
+      <c r="T30" s="369">
         <v>9.62</v>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       <c r="C31" t="str">
         <v>688227</v>
       </c>
-      <c r="D31" s="386" t="str">
+      <c r="D31" s="382" t="str">
         <v>净卖: -490.20万</v>
       </c>
       <c r="E31">
@@ -12126,37 +12126,37 @@
       <c r="I31" s="383">
         <v>0</v>
       </c>
-      <c r="J31" s="387">
+      <c r="J31" s="384">
         <v>19.99</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="385">
         <v>43.98</v>
       </c>
       <c r="L31" s="376">
         <v>71.32</v>
       </c>
-      <c r="M31" s="377">
+      <c r="M31" s="378">
         <v>67.14</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="386">
         <v>66.93</v>
       </c>
-      <c r="O31" s="381">
+      <c r="O31" s="387">
         <v>64.79</v>
       </c>
-      <c r="P31" s="385">
+      <c r="P31" s="379">
         <v>48.94</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="388">
         <v>50.96</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="377">
         <v>40.37</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="380">
         <v>43</v>
       </c>
-      <c r="T31" s="380">
+      <c r="T31" s="381">
         <v>106.77</v>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       <c r="C32" t="str">
         <v>002565</v>
       </c>
-      <c r="D32" s="392" t="str">
+      <c r="D32" s="400" t="str">
         <v>净卖: -2942.55万</v>
       </c>
       <c r="E32">
@@ -12188,37 +12188,37 @@
       <c r="I32" s="393">
         <v>-0.4</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="390">
         <v>-1.75</v>
       </c>
-      <c r="K32" s="397">
+      <c r="K32" s="398">
         <v>8.08</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="394">
         <v>18.84</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="391">
         <v>30.69</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="392">
         <v>43.74</v>
       </c>
-      <c r="O32" s="389">
+      <c r="O32" s="395">
         <v>45.63</v>
       </c>
-      <c r="P32" s="398">
+      <c r="P32" s="401">
         <v>60.16</v>
       </c>
-      <c r="Q32" s="391">
+      <c r="Q32" s="399">
         <v>76.18</v>
       </c>
       <c r="R32" s="396">
         <v>77.66</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="389">
         <v>81.29</v>
       </c>
-      <c r="T32" s="390">
+      <c r="T32" s="397">
         <v>154.64</v>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       <c r="C33" t="str">
         <v>920826</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="410" t="str">
         <v>净买: 408.58万</v>
       </c>
       <c r="E33">
@@ -12247,40 +12247,40 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="411">
         <v>3.25</v>
       </c>
       <c r="J33" s="405">
         <v>-3.4</v>
       </c>
-      <c r="K33" s="402">
+      <c r="K33" s="406">
         <v>-2.17</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="408">
         <v>-0.65</v>
       </c>
       <c r="M33" s="403">
         <v>-2.46</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="404">
         <v>-2.6</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="409">
         <v>-0.94</v>
       </c>
-      <c r="P33" s="409">
+      <c r="P33" s="407">
         <v>-1.37</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="412">
         <v>0.58</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="413">
         <v>4.63</v>
       </c>
-      <c r="S33" s="413">
+      <c r="S33" s="414">
         <v>3.54</v>
       </c>
-      <c r="T33" s="411">
+      <c r="T33" s="402">
         <v>-21.26</v>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       <c r="C34" t="str">
         <v>603122</v>
       </c>
-      <c r="D34" s="418" t="str">
+      <c r="D34" s="422" t="str">
         <v>净卖: -1862.43万</v>
       </c>
       <c r="E34">
@@ -12309,40 +12309,40 @@
       <c r="H34">
         <v>-6.1</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="415">
         <v>-4.17</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="421">
         <v>0.5</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="416">
         <v>10.54</v>
       </c>
       <c r="L34" s="423">
         <v>21.58</v>
       </c>
-      <c r="M34" s="424">
+      <c r="M34" s="425">
         <v>13.25</v>
       </c>
-      <c r="N34" s="416">
+      <c r="N34" s="417">
         <v>16.25</v>
       </c>
-      <c r="O34" s="421">
+      <c r="O34" s="426">
         <v>9.79</v>
       </c>
-      <c r="P34" s="426">
+      <c r="P34" s="418">
         <v>5.25</v>
       </c>
-      <c r="Q34" s="422">
+      <c r="Q34" s="419">
         <v>11.67</v>
       </c>
-      <c r="R34" s="417">
+      <c r="R34" s="427">
         <v>9.17</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="420">
         <v>14.38</v>
       </c>
-      <c r="T34" s="415">
+      <c r="T34" s="424">
         <v>-32.67</v>
       </c>
     </row>
@@ -12356,7 +12356,7 @@
       <c r="C35" t="str">
         <v>920504</v>
       </c>
-      <c r="D35" s="434" t="str">
+      <c r="D35" s="430" t="str">
         <v>净卖: -532.20万</v>
       </c>
       <c r="E35">
@@ -12371,40 +12371,40 @@
       <c r="H35">
         <v>6.26</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="431">
         <v>5.9</v>
       </c>
-      <c r="J35" s="439">
+      <c r="J35" s="435">
         <v>2.61</v>
       </c>
-      <c r="K35" s="440">
+      <c r="K35" s="438">
         <v>3.96</v>
       </c>
-      <c r="L35" s="428">
+      <c r="L35" s="440">
         <v>-1.42</v>
       </c>
-      <c r="M35" s="429">
+      <c r="M35" s="432">
         <v>-2.72</v>
       </c>
-      <c r="N35" s="436">
+      <c r="N35" s="433">
         <v>-3.17</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="439">
         <v>-2.57</v>
       </c>
-      <c r="P35" s="432">
+      <c r="P35" s="434">
         <v>-2.24</v>
       </c>
-      <c r="Q35" s="433">
+      <c r="Q35" s="428">
         <v>0.3</v>
       </c>
-      <c r="R35" s="437">
+      <c r="R35" s="436">
         <v>1.04</v>
       </c>
-      <c r="S35" s="431">
+      <c r="S35" s="437">
         <v>1.08</v>
       </c>
-      <c r="T35" s="438">
+      <c r="T35" s="429">
         <v>-15.75</v>
       </c>
     </row>
@@ -12418,7 +12418,7 @@
       <c r="C36" t="str">
         <v>601616</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="443" t="str">
         <v>净卖: -1517.47万</v>
       </c>
       <c r="E36">
@@ -12433,37 +12433,37 @@
       <c r="H36">
         <v>4.8</v>
       </c>
-      <c r="I36" s="452">
+      <c r="I36" s="451">
         <v>5</v>
       </c>
-      <c r="J36" s="453">
+      <c r="J36" s="444">
         <v>15.42</v>
       </c>
-      <c r="K36" s="447">
+      <c r="K36" s="452">
         <v>26.88</v>
       </c>
-      <c r="L36" s="448">
+      <c r="L36" s="445">
         <v>21.25</v>
       </c>
-      <c r="M36" s="441">
+      <c r="M36" s="453">
         <v>21.25</v>
       </c>
-      <c r="N36" s="443">
+      <c r="N36" s="441">
         <v>11.04</v>
       </c>
       <c r="O36" s="449">
         <v>8.33</v>
       </c>
-      <c r="P36" s="444">
+      <c r="P36" s="446">
         <v>7.08</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="450">
         <v>3.33</v>
       </c>
-      <c r="R36" s="446">
+      <c r="R36" s="447">
         <v>2.08</v>
       </c>
-      <c r="S36" s="450">
+      <c r="S36" s="448">
         <v>12.29</v>
       </c>
       <c r="T36" s="442">
@@ -12480,7 +12480,7 @@
       <c r="C37" t="str">
         <v>920471</v>
       </c>
-      <c r="D37" s="462" t="str">
+      <c r="D37" s="461" t="str">
         <v>净卖: -990.93万</v>
       </c>
       <c r="E37">
@@ -12498,37 +12498,37 @@
       <c r="I37" s="455">
         <v>29.46</v>
       </c>
-      <c r="J37" s="466">
+      <c r="J37" s="459">
         <v>33.16</v>
       </c>
-      <c r="K37" s="463">
+      <c r="K37" s="460">
         <v>26.05</v>
       </c>
-      <c r="L37" s="454">
+      <c r="L37" s="462">
         <v>32.79</v>
       </c>
       <c r="M37" s="456">
         <v>40.78</v>
       </c>
-      <c r="N37" s="458">
+      <c r="N37" s="463">
         <v>27.02</v>
       </c>
-      <c r="O37" s="459">
+      <c r="O37" s="464">
         <v>35.83</v>
       </c>
-      <c r="P37" s="460">
+      <c r="P37" s="465">
         <v>53.07</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="466">
         <v>57.29</v>
       </c>
-      <c r="R37" s="464">
+      <c r="R37" s="457">
         <v>37.45</v>
       </c>
-      <c r="S37" s="461">
+      <c r="S37" s="458">
         <v>44.26</v>
       </c>
-      <c r="T37" s="465">
+      <c r="T37" s="454">
         <v>-4.81</v>
       </c>
     </row>
@@ -12557,40 +12557,40 @@
       <c r="H38">
         <v>5.63</v>
       </c>
-      <c r="I38" s="468">
+      <c r="I38" s="471">
         <v>12.67</v>
       </c>
-      <c r="J38" s="469">
+      <c r="J38" s="474">
         <v>16</v>
       </c>
       <c r="K38" s="477">
         <v>10.67</v>
       </c>
-      <c r="L38" s="472">
+      <c r="L38" s="478">
         <v>32.8</v>
       </c>
-      <c r="M38" s="470">
+      <c r="M38" s="467">
         <v>36.67</v>
       </c>
-      <c r="N38" s="473">
+      <c r="N38" s="475">
         <v>44.23</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="468">
         <v>25.5</v>
       </c>
-      <c r="P38" s="478">
+      <c r="P38" s="479">
         <v>30.87</v>
       </c>
-      <c r="Q38" s="471">
+      <c r="Q38" s="469">
         <v>24.5</v>
       </c>
-      <c r="R38" s="479">
+      <c r="R38" s="472">
         <v>26</v>
       </c>
-      <c r="S38" s="475">
+      <c r="S38" s="470">
         <v>41</v>
       </c>
-      <c r="T38" s="467">
+      <c r="T38" s="473">
         <v>-17.47</v>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
       <c r="C39" t="str">
         <v>920414</v>
       </c>
-      <c r="D39" s="487" t="str">
+      <c r="D39" s="485" t="str">
         <v>净卖: -1486.22万</v>
       </c>
       <c r="E39">
@@ -12619,40 +12619,40 @@
       <c r="H39">
         <v>0.68</v>
       </c>
-      <c r="I39" s="483">
+      <c r="I39" s="490">
         <v>29.11</v>
       </c>
-      <c r="J39" s="484">
+      <c r="J39" s="487">
         <v>33.83</v>
       </c>
-      <c r="K39" s="480">
+      <c r="K39" s="491">
         <v>44.34</v>
       </c>
-      <c r="L39" s="488">
+      <c r="L39" s="492">
         <v>28.73</v>
       </c>
-      <c r="M39" s="481">
+      <c r="M39" s="488">
         <v>21.38</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="480">
         <v>13.28</v>
       </c>
-      <c r="O39" s="489">
+      <c r="O39" s="486">
         <v>14.93</v>
       </c>
-      <c r="P39" s="490">
+      <c r="P39" s="489">
         <v>28.43</v>
       </c>
-      <c r="Q39" s="485">
+      <c r="Q39" s="482">
         <v>45.16</v>
       </c>
-      <c r="R39" s="491">
+      <c r="R39" s="483">
         <v>27.01</v>
       </c>
-      <c r="S39" s="492">
+      <c r="S39" s="481">
         <v>29.63</v>
       </c>
-      <c r="T39" s="486">
+      <c r="T39" s="484">
         <v>-2.25</v>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       <c r="C40" t="str">
         <v>920414</v>
       </c>
-      <c r="D40" s="495" t="str">
+      <c r="D40" s="501" t="str">
         <v>净卖: -1162.25万</v>
       </c>
       <c r="E40">
@@ -12681,40 +12681,40 @@
       <c r="H40">
         <v>-9.19</v>
       </c>
-      <c r="I40" s="501">
+      <c r="I40" s="498">
         <v>18.77</v>
       </c>
-      <c r="J40" s="496">
+      <c r="J40" s="504">
         <v>5.93</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="505">
         <v>-0.12</v>
       </c>
-      <c r="L40" s="504">
+      <c r="L40" s="495">
         <v>-6.79</v>
       </c>
-      <c r="M40" s="497">
+      <c r="M40" s="493">
         <v>-5.43</v>
       </c>
-      <c r="N40" s="498">
+      <c r="N40" s="502">
         <v>5.68</v>
       </c>
       <c r="O40" s="494">
         <v>19.44</v>
       </c>
-      <c r="P40" s="505">
+      <c r="P40" s="496">
         <v>4.51</v>
       </c>
-      <c r="Q40" s="503">
+      <c r="Q40" s="499">
         <v>6.67</v>
       </c>
-      <c r="R40" s="499">
+      <c r="R40" s="500">
         <v>9.26</v>
       </c>
-      <c r="S40" s="500">
+      <c r="S40" s="503">
         <v>8.09</v>
       </c>
-      <c r="T40" s="493">
+      <c r="T40" s="497">
         <v>-19.57</v>
       </c>
     </row>
@@ -12743,40 +12743,40 @@
       <c r="H41">
         <v>-6.81</v>
       </c>
-      <c r="I41" s="517">
+      <c r="I41" s="509">
         <v>-4.29</v>
       </c>
-      <c r="J41" s="509">
+      <c r="J41" s="512">
         <v>-9.76</v>
       </c>
       <c r="K41" s="513">
         <v>-15.78</v>
       </c>
-      <c r="L41" s="518">
+      <c r="L41" s="515">
         <v>-14.56</v>
       </c>
-      <c r="M41" s="506">
+      <c r="M41" s="510">
         <v>-4.52</v>
       </c>
-      <c r="N41" s="515">
+      <c r="N41" s="511">
         <v>7.92</v>
       </c>
-      <c r="O41" s="516">
+      <c r="O41" s="517">
         <v>-5.58</v>
       </c>
-      <c r="P41" s="510">
+      <c r="P41" s="518">
         <v>-3.63</v>
       </c>
-      <c r="Q41" s="507">
+      <c r="Q41" s="506">
         <v>-1.28</v>
       </c>
-      <c r="R41" s="508">
+      <c r="R41" s="507">
         <v>-2.34</v>
       </c>
-      <c r="S41" s="511">
+      <c r="S41" s="508">
         <v>-8.25</v>
       </c>
-      <c r="T41" s="512">
+      <c r="T41" s="516">
         <v>-27.33</v>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       <c r="C42" t="str">
         <v>001376</v>
       </c>
-      <c r="D42" s="524" t="str">
+      <c r="D42" s="525" t="str">
         <v>净卖: -998.65万</v>
       </c>
       <c r="E42">
@@ -12805,40 +12805,40 @@
       <c r="H42">
         <v>4.53</v>
       </c>
-      <c r="I42" s="520">
+      <c r="I42" s="526">
         <v>5.24</v>
       </c>
-      <c r="J42" s="521">
+      <c r="J42" s="522">
         <v>1.85</v>
       </c>
-      <c r="K42" s="525">
+      <c r="K42" s="523">
         <v>-5.24</v>
       </c>
-      <c r="L42" s="526">
+      <c r="L42" s="529">
         <v>-8.63</v>
       </c>
-      <c r="M42" s="530">
+      <c r="M42" s="524">
         <v>-11.16</v>
       </c>
-      <c r="N42" s="522">
+      <c r="N42" s="527">
         <v>-15.62</v>
       </c>
-      <c r="O42" s="531">
+      <c r="O42" s="528">
         <v>-14.59</v>
       </c>
-      <c r="P42" s="523">
+      <c r="P42" s="531">
         <v>-14.81</v>
       </c>
       <c r="Q42" s="519">
         <v>-17.55</v>
       </c>
-      <c r="R42" s="528">
+      <c r="R42" s="530">
         <v>-9.31</v>
       </c>
-      <c r="S42" s="529">
+      <c r="S42" s="520">
         <v>-12.45</v>
       </c>
-      <c r="T42" s="527">
+      <c r="T42" s="521">
         <v>-30.99</v>
       </c>
     </row>
@@ -12867,16 +12867,16 @@
       <c r="H43">
         <v>-5.9</v>
       </c>
-      <c r="I43" s="532">
+      <c r="I43" s="534">
         <v>-4.41</v>
       </c>
-      <c r="J43" s="536">
+      <c r="J43" s="540">
         <v>-2.55</v>
       </c>
-      <c r="K43" s="543">
+      <c r="K43" s="535">
         <v>7.19</v>
       </c>
-      <c r="L43" s="533">
+      <c r="L43" s="536">
         <v>17.87</v>
       </c>
       <c r="M43" s="537">
@@ -12885,22 +12885,22 @@
       <c r="N43" s="544">
         <v>18.33</v>
       </c>
-      <c r="O43" s="534">
+      <c r="O43" s="532">
         <v>13.69</v>
       </c>
-      <c r="P43" s="540">
+      <c r="P43" s="542">
         <v>11.6</v>
       </c>
-      <c r="Q43" s="541">
+      <c r="Q43" s="538">
         <v>5.57</v>
       </c>
-      <c r="R43" s="538">
+      <c r="R43" s="543">
         <v>3.25</v>
       </c>
-      <c r="S43" s="542">
+      <c r="S43" s="533">
         <v>13.69</v>
       </c>
-      <c r="T43" s="535">
+      <c r="T43" s="541">
         <v>-9.98</v>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       <c r="C44" t="str">
         <v>920299</v>
       </c>
-      <c r="D44" s="557" t="str">
+      <c r="D44" s="545" t="str">
         <v>净卖: -590.29万</v>
       </c>
       <c r="E44">
@@ -12929,40 +12929,40 @@
       <c r="H44">
         <v>-0.87</v>
       </c>
-      <c r="I44" s="552">
+      <c r="I44" s="551">
         <v>10.93</v>
       </c>
-      <c r="J44" s="545">
+      <c r="J44" s="546">
         <v>7.07</v>
       </c>
-      <c r="K44" s="556">
+      <c r="K44" s="552">
         <v>4.57</v>
       </c>
       <c r="L44" s="547">
         <v>8.44</v>
       </c>
-      <c r="M44" s="548">
+      <c r="M44" s="553">
         <v>4.89</v>
       </c>
-      <c r="N44" s="553">
+      <c r="N44" s="554">
         <v>1.09</v>
       </c>
-      <c r="O44" s="549">
+      <c r="O44" s="555">
         <v>-1.2</v>
       </c>
-      <c r="P44" s="546">
+      <c r="P44" s="549">
         <v>-0.42</v>
       </c>
-      <c r="Q44" s="554">
+      <c r="Q44" s="548">
         <v>-2.85</v>
       </c>
-      <c r="R44" s="550">
+      <c r="R44" s="556">
         <v>-4.75</v>
       </c>
-      <c r="S44" s="551">
+      <c r="S44" s="557">
         <v>-4.08</v>
       </c>
-      <c r="T44" s="555">
+      <c r="T44" s="550">
         <v>-12.44</v>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       <c r="C45" t="str">
         <v>688079</v>
       </c>
-      <c r="D45" s="561" t="str">
+      <c r="D45" s="558" t="str">
         <v>净卖: -1226.18万</v>
       </c>
       <c r="E45">
@@ -12991,40 +12991,40 @@
       <c r="H45">
         <v>4.51</v>
       </c>
-      <c r="I45" s="568">
+      <c r="I45" s="570">
         <v>14.78</v>
       </c>
-      <c r="J45" s="569">
+      <c r="J45" s="565">
         <v>9.3</v>
       </c>
-      <c r="K45" s="562">
+      <c r="K45" s="561">
         <v>11.46</v>
       </c>
       <c r="L45" s="559">
         <v>13.87</v>
       </c>
-      <c r="M45" s="570">
+      <c r="M45" s="566">
         <v>15.37</v>
       </c>
-      <c r="N45" s="563">
+      <c r="N45" s="560">
         <v>18.69</v>
       </c>
-      <c r="O45" s="566">
+      <c r="O45" s="567">
         <v>12.96</v>
       </c>
-      <c r="P45" s="560">
+      <c r="P45" s="562">
         <v>11.3</v>
       </c>
-      <c r="Q45" s="564">
+      <c r="Q45" s="568">
         <v>5.81</v>
       </c>
-      <c r="R45" s="567">
+      <c r="R45" s="563">
         <v>8.72</v>
       </c>
-      <c r="S45" s="565">
+      <c r="S45" s="564">
         <v>4.57</v>
       </c>
-      <c r="T45" s="558">
+      <c r="T45" s="569">
         <v>34.97</v>
       </c>
     </row>
@@ -13053,40 +13053,40 @@
       <c r="H46">
         <v>0.99</v>
       </c>
-      <c r="I46" s="574">
+      <c r="I46" s="578">
         <v>13.48</v>
       </c>
-      <c r="J46" s="575">
+      <c r="J46" s="579">
         <v>9.11</v>
       </c>
-      <c r="K46" s="581">
+      <c r="K46" s="580">
         <v>-1.68</v>
       </c>
-      <c r="L46" s="571">
+      <c r="L46" s="583">
         <v>2.25</v>
       </c>
-      <c r="M46" s="582">
+      <c r="M46" s="571">
         <v>-5.86</v>
       </c>
-      <c r="N46" s="576">
+      <c r="N46" s="572">
         <v>-3.8</v>
       </c>
-      <c r="O46" s="579">
+      <c r="O46" s="576">
         <v>-7.84</v>
       </c>
       <c r="P46" s="577">
         <v>-9.84</v>
       </c>
-      <c r="Q46" s="583">
+      <c r="Q46" s="581">
         <v>-14.77</v>
       </c>
-      <c r="R46" s="580">
+      <c r="R46" s="582">
         <v>-9.43</v>
       </c>
-      <c r="S46" s="572">
+      <c r="S46" s="574">
         <v>-9.64</v>
       </c>
-      <c r="T46" s="578">
+      <c r="T46" s="575">
         <v>-12.39</v>
       </c>
     </row>
@@ -13100,7 +13100,7 @@
       <c r="C47" t="str">
         <v>688485</v>
       </c>
-      <c r="D47" s="593" t="str">
+      <c r="D47" s="586" t="str">
         <v>净买: 1305.22万</v>
       </c>
       <c r="E47">
@@ -13115,40 +13115,40 @@
       <c r="H47">
         <v>-6.79</v>
       </c>
-      <c r="I47" s="584">
+      <c r="I47" s="595">
         <v>0.15</v>
       </c>
-      <c r="J47" s="585">
+      <c r="J47" s="587">
         <v>-7.77</v>
       </c>
-      <c r="K47" s="594">
+      <c r="K47" s="590">
         <v>-7.32</v>
       </c>
-      <c r="L47" s="586">
+      <c r="L47" s="588">
         <v>-2.61</v>
       </c>
-      <c r="M47" s="595">
+      <c r="M47" s="596">
         <v>16.88</v>
       </c>
-      <c r="N47" s="596">
+      <c r="N47" s="591">
         <v>25.13</v>
       </c>
-      <c r="O47" s="587">
+      <c r="O47" s="592">
         <v>50.15</v>
       </c>
-      <c r="P47" s="588">
+      <c r="P47" s="593">
         <v>48.24</v>
       </c>
-      <c r="Q47" s="589">
+      <c r="Q47" s="594">
         <v>51.23</v>
       </c>
-      <c r="R47" s="590">
+      <c r="R47" s="584">
         <v>65.42</v>
       </c>
-      <c r="S47" s="592">
+      <c r="S47" s="589">
         <v>59.86</v>
       </c>
-      <c r="T47" s="591">
+      <c r="T47" s="585">
         <v>62.43</v>
       </c>
     </row>
@@ -13211,40 +13211,40 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="599">
+      <c r="I49" s="606">
         <v>78.26</v>
       </c>
-      <c r="J49" s="600">
+      <c r="J49" s="607">
         <v>80.43</v>
       </c>
-      <c r="K49" s="606">
+      <c r="K49" s="599">
         <v>76.09</v>
       </c>
-      <c r="L49" s="604">
+      <c r="L49" s="608">
         <v>71.74</v>
       </c>
-      <c r="M49" s="601">
+      <c r="M49" s="597">
         <v>69.57</v>
       </c>
-      <c r="N49" s="607">
+      <c r="N49" s="601">
         <v>69.57</v>
       </c>
-      <c r="O49" s="608">
+      <c r="O49" s="598">
         <v>63.04</v>
       </c>
-      <c r="P49" s="597">
+      <c r="P49" s="602">
         <v>69.57</v>
       </c>
-      <c r="Q49" s="598">
+      <c r="Q49" s="603">
         <v>71.74</v>
       </c>
-      <c r="R49" s="602">
+      <c r="R49" s="604">
         <v>75.56</v>
       </c>
       <c r="S49" s="605">
         <v>80</v>
       </c>
-      <c r="T49" s="603">
+      <c r="T49" s="600">
         <v>43.48</v>
       </c>
     </row>
@@ -13262,37 +13262,37 @@
       <c r="I50" s="617">
         <v>8.72</v>
       </c>
-      <c r="J50" s="612">
+      <c r="J50" s="613">
         <v>8.72</v>
       </c>
-      <c r="K50" s="619">
+      <c r="K50" s="614">
         <v>8.24</v>
       </c>
-      <c r="L50" s="613">
+      <c r="L50" s="618">
         <v>10.18</v>
       </c>
-      <c r="M50" s="614">
+      <c r="M50" s="620">
         <v>11.36</v>
       </c>
-      <c r="N50" s="620">
+      <c r="N50" s="610">
         <v>10.81</v>
       </c>
-      <c r="O50" s="609">
+      <c r="O50" s="611">
         <v>11.29</v>
       </c>
-      <c r="P50" s="610">
+      <c r="P50" s="615">
         <v>11.98</v>
       </c>
-      <c r="Q50" s="615">
+      <c r="Q50" s="616">
         <v>12.74</v>
       </c>
-      <c r="R50" s="611">
+      <c r="R50" s="619">
         <v>14.57</v>
       </c>
-      <c r="S50" s="618">
+      <c r="S50" s="612">
         <v>16.24</v>
       </c>
-      <c r="T50" s="616">
+      <c r="T50" s="609">
         <v>12.06</v>
       </c>
     </row>

--- a/youzi/北京帮/index.xlsx
+++ b/youzi/北京帮/index.xlsx
@@ -39,115 +39,3367 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3747"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECD7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8C95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4B59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF71C484"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E0E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46571"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9F6EC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7F0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66F7B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E6CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A143"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3CAF56"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9AD5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62BF77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,421 +3429,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3747"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECD7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FFB6E1C0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,7 +3483,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -615,211 +3519,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8C95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15462"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -831,481 +3543,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4B59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF71C484"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E0E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF72C585"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1317,2293 +3627,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D9DC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46571"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9CD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7F0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E6CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66F7B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA91E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC1E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A143"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9AD5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3CAF56"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62BF77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3621,61 +3657,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF72C585"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -10314,7 +10314,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -3320.73万</v>
       </c>
       <c r="E2">
@@ -10332,37 +10332,37 @@
       <c r="I2" s="7">
         <v>0</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="1">
         <v>2.04</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="4">
         <v>4.88</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="11">
         <v>7.07</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="5">
         <v>7.94</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="2">
         <v>10.06</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="8">
         <v>21.06</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="3">
         <v>23.03</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="12">
         <v>25.8</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="13">
         <v>24.05</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="10">
         <v>-32</v>
       </c>
     </row>
@@ -10376,7 +10376,7 @@
       <c r="C3" t="str">
         <v>000710</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -1108.14万</v>
       </c>
       <c r="E3">
@@ -10391,10 +10391,10 @@
       <c r="H3">
         <v>-0.08</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="20">
         <v>10.1</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="21">
         <v>21.13</v>
       </c>
       <c r="K3" s="17">
@@ -10403,28 +10403,28 @@
       <c r="L3" s="22">
         <v>30.85</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="25">
         <v>34.5</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="26">
         <v>40.64</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="14">
         <v>46.7</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="23">
         <v>42.19</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="24">
         <v>33.49</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="18">
         <v>34.19</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="15">
         <v>25.8</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="19">
         <v>-21.83</v>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       <c r="C4" t="str">
         <v>601616</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -513.00万</v>
       </c>
       <c r="E4">
@@ -10453,40 +10453,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <v>9.62</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="30">
         <v>6.41</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>7.26</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="35">
         <v>5.34</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="38">
         <v>7.69</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="39">
         <v>7.91</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="36">
         <v>7.69</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="34">
         <v>3.85</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="27">
         <v>0.43</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="37">
         <v>2.35</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="32">
         <v>4.27</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="33">
         <v>2.78</v>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       <c r="C5" t="str">
         <v>600370</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -194.00万</v>
       </c>
       <c r="E5">
@@ -10515,40 +10515,40 @@
       <c r="H5">
         <v>-1.14</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="41">
         <v>11.49</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="47">
         <v>22.41</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="40">
         <v>16.09</v>
       </c>
       <c r="L5" s="42">
         <v>27.59</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="43">
         <v>25.29</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="44">
         <v>20.11</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="48">
         <v>14.37</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="45">
         <v>2.87</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="49">
         <v>-5.75</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="50">
         <v>-5.75</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="51">
         <v>-3.45</v>
       </c>
-      <c r="T5" s="46">
+      <c r="T5" s="52">
         <v>37.93</v>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       <c r="C6" t="str">
         <v>603123</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -3403.34万</v>
       </c>
       <c r="E6">
@@ -10577,40 +10577,40 @@
       <c r="H6">
         <v>-6.28</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="63">
         <v>17.38</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="64">
         <v>8.2</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="58">
         <v>5.96</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="65">
         <v>0.41</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="57">
         <v>3.31</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="53">
         <v>-2.15</v>
       </c>
       <c r="O6" s="54">
         <v>-7.95</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="55">
         <v>-2.15</v>
       </c>
-      <c r="Q6" s="55">
+      <c r="Q6" s="59">
         <v>-0.66</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="60">
         <v>9.27</v>
       </c>
       <c r="S6" s="61">
         <v>2.57</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="56">
         <v>2.73</v>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       <c r="C7" t="str">
         <v>603616</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -196.32万</v>
       </c>
       <c r="E7">
@@ -10639,40 +10639,40 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="71">
         <v>10.12</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="67">
         <v>8.4</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="68">
         <v>12.35</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="69">
         <v>14.07</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="75">
         <v>12.84</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="66">
         <v>24.2</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="72">
         <v>18.27</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="76">
         <v>13.58</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="77">
         <v>12.35</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="70">
         <v>14.07</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="78">
         <v>10.86</v>
       </c>
-      <c r="T7" s="74">
+      <c r="T7" s="73">
         <v>57.28</v>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       <c r="C8" t="str">
         <v>600399</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -1684.57万</v>
       </c>
       <c r="E8">
@@ -10701,37 +10701,37 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="86">
         <v>10.06</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="83">
         <v>5.69</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="84">
         <v>4.93</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="81">
         <v>7.59</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="87">
         <v>5.69</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="89">
         <v>5.88</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="90">
         <v>10.44</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="91">
         <v>13.47</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="82">
         <v>11.01</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="79">
         <v>13.47</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="80">
         <v>13.28</v>
       </c>
       <c r="T8" s="85">
@@ -10748,7 +10748,7 @@
       <c r="C9" t="str">
         <v>605099</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="94" t="str">
         <v>净买: 320.21万</v>
       </c>
       <c r="E9">
@@ -10763,40 +10763,40 @@
       <c r="H9">
         <v>-9.03</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="100">
         <v>-1.06</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="101">
         <v>-9.31</v>
       </c>
       <c r="K9" s="97">
         <v>-12.01</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="92">
         <v>-13.02</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="93">
         <v>-12.9</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="95">
         <v>-14.41</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="98">
         <v>-14.02</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="96">
         <v>-14.24</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="102">
         <v>-12.96</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="103">
         <v>-11.51</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="99">
         <v>-12.1</v>
       </c>
-      <c r="T9" s="95">
+      <c r="T9" s="104">
         <v>12.07</v>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       <c r="C10" t="str">
         <v>600581</v>
       </c>
-      <c r="D10" s="112" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -685.48万</v>
       </c>
       <c r="E10">
@@ -10825,40 +10825,40 @@
       <c r="H10">
         <v>-0.26</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="106">
         <v>10.42</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="110">
         <v>21.35</v>
       </c>
-      <c r="K10" s="117">
+      <c r="K10" s="114">
         <v>33.59</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="107">
         <v>36.2</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="108">
         <v>22.66</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="109">
         <v>15.89</v>
       </c>
       <c r="O10" s="115">
         <v>16.41</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="116">
         <v>16.15</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="117">
         <v>19.79</v>
       </c>
-      <c r="R10" s="106">
+      <c r="R10" s="112">
         <v>17.19</v>
       </c>
-      <c r="S10" s="111">
+      <c r="S10" s="105">
         <v>17.97</v>
       </c>
-      <c r="T10" s="116">
+      <c r="T10" s="111">
         <v>-21.09</v>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       <c r="C11" t="str">
         <v>836504</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -1178.54万</v>
       </c>
       <c r="E11">
@@ -10887,40 +10887,40 @@
       <c r="H11">
         <v>1.46</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="123">
         <v>16.5</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="119">
         <v>6.23</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="120">
         <v>6.44</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="124">
         <v>3.7</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="125">
         <v>4.21</v>
       </c>
       <c r="N11" s="121">
         <v>1.81</v>
       </c>
-      <c r="O11" s="125">
+      <c r="O11" s="127">
         <v>-0.75</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="128">
         <v>0.24</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="129">
         <v>0.48</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="126">
         <v>2.02</v>
       </c>
-      <c r="S11" s="127">
+      <c r="S11" s="130">
         <v>2.84</v>
       </c>
-      <c r="T11" s="122">
+      <c r="T11" s="118">
         <v>-5.07</v>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
       <c r="C12" t="str">
         <v>836504</v>
       </c>
-      <c r="D12" s="132" t="str">
+      <c r="D12" s="131" t="str">
         <v>净买: 584.91万</v>
       </c>
       <c r="E12">
@@ -10949,40 +10949,40 @@
       <c r="H12">
         <v>-5.97</v>
       </c>
-      <c r="I12" s="133">
+      <c r="I12" s="141">
         <v>-3.03</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="137">
         <v>-2.84</v>
       </c>
-      <c r="K12" s="134">
+      <c r="K12" s="132">
         <v>-5.34</v>
       </c>
       <c r="L12" s="139">
         <v>-4.87</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="133">
         <v>-7.06</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="142">
         <v>-9.41</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="143">
         <v>-8.5</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="134">
         <v>-8.28</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="135">
         <v>-6.87</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="140">
         <v>-6.13</v>
       </c>
-      <c r="S12" s="142">
+      <c r="S12" s="136">
         <v>-10.38</v>
       </c>
-      <c r="T12" s="143">
+      <c r="T12" s="138">
         <v>-13.34</v>
       </c>
     </row>
@@ -10996,7 +10996,7 @@
       <c r="C13" t="str">
         <v>873679</v>
       </c>
-      <c r="D13" s="144" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -359.87万</v>
       </c>
       <c r="E13">
@@ -11011,40 +11011,40 @@
       <c r="H13">
         <v>1.77</v>
       </c>
-      <c r="I13" s="149">
+      <c r="I13" s="154">
         <v>7.59</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="155">
         <v>7.75</v>
       </c>
-      <c r="K13" s="152">
+      <c r="K13" s="150">
         <v>1.45</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="151">
         <v>-3.03</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="156">
         <v>-6.09</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="146">
         <v>-4.27</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="153">
         <v>-0.5</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="147">
         <v>1.08</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="148">
         <v>4.19</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="144">
         <v>-2.78</v>
       </c>
-      <c r="S13" s="151">
+      <c r="S13" s="152">
         <v>4.44</v>
       </c>
-      <c r="T13" s="155">
+      <c r="T13" s="149">
         <v>-5.64</v>
       </c>
     </row>
@@ -11073,40 +11073,40 @@
       <c r="H14">
         <v>6.91</v>
       </c>
-      <c r="I14" s="158">
+      <c r="I14" s="165">
         <v>2.92</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="162">
         <v>12.54</v>
       </c>
-      <c r="K14" s="159">
+      <c r="K14" s="163">
         <v>18.46</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="157">
         <v>15</v>
       </c>
-      <c r="M14" s="161">
+      <c r="M14" s="158">
         <v>14.23</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="159">
         <v>19.31</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="160">
         <v>22.23</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="166">
         <v>11.46</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="168">
         <v>2.38</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="161">
         <v>6.15</v>
       </c>
-      <c r="S14" s="165">
+      <c r="S14" s="169">
         <v>7.92</v>
       </c>
-      <c r="T14" s="166">
+      <c r="T14" s="164">
         <v>150.38</v>
       </c>
     </row>
@@ -11120,7 +11120,7 @@
       <c r="C15" t="str">
         <v>688228</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="177" t="str">
         <v>净卖: -2485.38万</v>
       </c>
       <c r="E15">
@@ -11135,40 +11135,40 @@
       <c r="H15">
         <v>12.58</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="178">
         <v>3.13</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="171">
         <v>20.16</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="179">
         <v>13.29</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="172">
         <v>1.3</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="180">
         <v>1.88</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="173">
         <v>-10.94</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="181">
         <v>-8.2</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="175">
         <v>-3.3</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="182">
         <v>-0.78</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="174">
         <v>4.05</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="176">
         <v>10.16</v>
       </c>
-      <c r="T15" s="182">
+      <c r="T15" s="170">
         <v>-14.13</v>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       <c r="C16" t="str">
         <v>688228</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="193" t="str">
         <v>净卖: -1919.36万</v>
       </c>
       <c r="E16">
@@ -11197,40 +11197,40 @@
       <c r="H16">
         <v>-1.95</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="186">
         <v>18.84</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="194">
         <v>12.05</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="191">
         <v>0.19</v>
       </c>
-      <c r="L16" s="194">
+      <c r="L16" s="188">
         <v>0.76</v>
       </c>
-      <c r="M16" s="195">
+      <c r="M16" s="187">
         <v>-11.91</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="189">
         <v>-9.21</v>
       </c>
       <c r="O16" s="190">
         <v>-4.37</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="195">
         <v>-1.87</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="183">
         <v>2.91</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="192">
         <v>8.95</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="184">
         <v>24.35</v>
       </c>
-      <c r="T16" s="192">
+      <c r="T16" s="185">
         <v>-15.07</v>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       <c r="C17" t="str">
         <v>833580</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="202" t="str">
         <v>净卖: -905.56万</v>
       </c>
       <c r="E17">
@@ -11259,40 +11259,40 @@
       <c r="H17">
         <v>-0.89</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="205">
         <v>18.47</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="206">
         <v>27.43</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="197">
         <v>16.82</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="207">
         <v>16.4</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="208">
         <v>51.27</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="198">
         <v>37.28</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="196">
         <v>26.95</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="203">
         <v>22.67</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="199">
         <v>28.53</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="200">
         <v>36.39</v>
       </c>
-      <c r="S17" s="206">
+      <c r="S17" s="204">
         <v>33.01</v>
       </c>
-      <c r="T17" s="200">
+      <c r="T17" s="201">
         <v>11.65</v>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       <c r="C18" t="str">
         <v>836422</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="220" t="str">
         <v>净卖: -1044.29万</v>
       </c>
       <c r="E18">
@@ -11321,40 +11321,40 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="210">
         <v>29.97</v>
       </c>
-      <c r="J18" s="218">
+      <c r="J18" s="221">
         <v>33.59</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="214">
         <v>15.79</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="217">
         <v>11.13</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="215">
         <v>11.61</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="218">
         <v>9.25</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="216">
         <v>11.27</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="219">
         <v>9.74</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="211">
         <v>5.84</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="209">
         <v>8.55</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="212">
         <v>10.78</v>
       </c>
-      <c r="T18" s="209">
+      <c r="T18" s="213">
         <v>0</v>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       <c r="C19" t="str">
         <v>600157</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="232" t="str">
         <v>净卖: -4374.77万</v>
       </c>
       <c r="E19">
@@ -11383,37 +11383,37 @@
       <c r="H19">
         <v>1.94</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="233">
         <v>8.23</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="228">
         <v>6.96</v>
       </c>
       <c r="K19" s="234">
         <v>2.53</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="222">
         <v>8.86</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="223">
         <v>5.06</v>
       </c>
-      <c r="N19" s="232">
+      <c r="N19" s="225">
         <v>1.9</v>
       </c>
-      <c r="O19" s="225">
+      <c r="O19" s="226">
         <v>1.9</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="231">
         <v>2.53</v>
       </c>
       <c r="Q19" s="229">
         <v>3.16</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="230">
         <v>7.59</v>
       </c>
-      <c r="S19" s="233">
+      <c r="S19" s="224">
         <v>8.86</v>
       </c>
       <c r="T19" s="227">
@@ -11430,7 +11430,7 @@
       <c r="C20" t="str">
         <v>838030</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="245" t="str">
         <v>净卖: -909.25万</v>
       </c>
       <c r="E20">
@@ -11445,36 +11445,36 @@
       <c r="H20">
         <v>0.13</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="238">
         <v>29.83</v>
       </c>
-      <c r="J20" s="241">
+      <c r="J20" s="239">
         <v>13.53</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="235">
         <v>7.1</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="243">
         <v>4.99</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="240">
         <v>4.73</v>
       </c>
-      <c r="N20" s="245">
+      <c r="N20" s="236">
         <v>0.92</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="244">
         <v>0.79</v>
       </c>
-      <c r="P20" s="237">
+      <c r="P20" s="241">
         <v>0.53</v>
       </c>
-      <c r="Q20" s="238">
+      <c r="Q20" s="242">
         <v>-0.92</v>
       </c>
       <c r="R20" t="str"/>
       <c r="S20" t="str"/>
-      <c r="T20" s="239">
+      <c r="T20" s="237">
         <v>-0.92</v>
       </c>
     </row>
@@ -11503,40 +11503,40 @@
       <c r="H21">
         <v>-1.26</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="248">
         <v>11.49</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="246">
         <v>9.15</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="249">
         <v>8.72</v>
       </c>
-      <c r="L21" s="246">
+      <c r="L21" s="257">
         <v>7.66</v>
       </c>
-      <c r="M21" s="247">
+      <c r="M21" s="250">
         <v>7.87</v>
       </c>
-      <c r="N21" s="253">
+      <c r="N21" s="251">
         <v>10.85</v>
       </c>
-      <c r="O21" s="248">
+      <c r="O21" s="254">
         <v>17.66</v>
       </c>
-      <c r="P21" s="249">
+      <c r="P21" s="258">
         <v>17.45</v>
       </c>
-      <c r="Q21" s="255">
+      <c r="Q21" s="247">
         <v>29.15</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="252">
         <v>30.85</v>
       </c>
-      <c r="S21" s="250">
+      <c r="S21" s="253">
         <v>36.6</v>
       </c>
-      <c r="T21" s="257">
+      <c r="T21" s="255">
         <v>86.6</v>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       <c r="C22" t="str">
         <v>300818</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="268" t="str">
         <v>净卖: -913.45万</v>
       </c>
       <c r="E22">
@@ -11565,40 +11565,40 @@
       <c r="H22">
         <v>8.97</v>
       </c>
-      <c r="I22" s="259">
+      <c r="I22" s="269">
         <v>10.11</v>
       </c>
-      <c r="J22" s="265">
+      <c r="J22" s="264">
         <v>3.83</v>
       </c>
       <c r="K22" s="260">
         <v>3.12</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="270">
         <v>4.02</v>
       </c>
-      <c r="M22" s="266">
+      <c r="M22" s="265">
         <v>10.11</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="271">
         <v>6.05</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="261">
         <v>5.75</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="259">
         <v>13.23</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="262">
         <v>19.02</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="266">
         <v>14.17</v>
       </c>
-      <c r="S22" s="268">
+      <c r="S22" s="267">
         <v>11.5</v>
       </c>
-      <c r="T22" s="264">
+      <c r="T22" s="263">
         <v>33.35</v>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       <c r="C23" t="str">
         <v>601212</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="274" t="str">
         <v>净卖: -4295.10万</v>
       </c>
       <c r="E23">
@@ -11627,40 +11627,40 @@
       <c r="H23">
         <v>-0.39</v>
       </c>
-      <c r="I23" s="277">
+      <c r="I23" s="281">
         <v>10.47</v>
       </c>
       <c r="J23" s="282">
         <v>9.29</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="275">
         <v>6.72</v>
       </c>
-      <c r="L23" s="273">
+      <c r="L23" s="276">
         <v>17.39</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="277">
         <v>29.05</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="278">
         <v>16.21</v>
       </c>
-      <c r="O23" s="281">
+      <c r="O23" s="283">
         <v>11.46</v>
       </c>
-      <c r="P23" s="278">
+      <c r="P23" s="279">
         <v>6.32</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="284">
         <v>4.15</v>
       </c>
       <c r="R23" s="280">
         <v>2.77</v>
       </c>
-      <c r="S23" s="272">
+      <c r="S23" s="273">
         <v>4.74</v>
       </c>
-      <c r="T23" s="275">
+      <c r="T23" s="272">
         <v>59.29</v>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       <c r="C24" t="str">
         <v>600740</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="294" t="str">
         <v>净买: 1621.89万</v>
       </c>
       <c r="E24">
@@ -11689,40 +11689,40 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="286">
+      <c r="I24" s="288">
         <v>10.07</v>
       </c>
       <c r="J24" s="291">
         <v>1.92</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="287">
         <v>2.88</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="289">
         <v>4.32</v>
       </c>
-      <c r="M24" s="296">
+      <c r="M24" s="295">
         <v>6.71</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="290">
         <v>2.88</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="296">
         <v>2.4</v>
       </c>
-      <c r="P24" s="289">
+      <c r="P24" s="297">
         <v>4.08</v>
       </c>
-      <c r="Q24" s="293">
+      <c r="Q24" s="285">
         <v>3.36</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="286">
         <v>5.28</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="292">
         <v>6.95</v>
       </c>
-      <c r="T24" s="285">
+      <c r="T24" s="293">
         <v>-0.48</v>
       </c>
     </row>
@@ -11751,40 +11751,40 @@
       <c r="H25">
         <v>7.07</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="308">
         <v>2.8</v>
       </c>
-      <c r="J25" s="304">
+      <c r="J25" s="309">
         <v>13.09</v>
       </c>
       <c r="K25" s="305">
         <v>24.4</v>
       </c>
-      <c r="L25" s="298">
+      <c r="L25" s="306">
         <v>36.85</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="298">
         <v>50.57</v>
       </c>
-      <c r="N25" s="306">
+      <c r="N25" s="300">
         <v>65.69</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="301">
         <v>82.21</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="302">
         <v>100.38</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="310">
         <v>110.93</v>
       </c>
       <c r="R25" s="303">
         <v>132.02</v>
       </c>
-      <c r="S25" s="308">
+      <c r="S25" s="304">
         <v>155.27</v>
       </c>
-      <c r="T25" s="309">
+      <c r="T25" s="307">
         <v>105.34</v>
       </c>
     </row>
@@ -11798,7 +11798,7 @@
       <c r="C26" t="str">
         <v>002748</v>
       </c>
-      <c r="D26" s="322" t="str">
+      <c r="D26" s="315" t="str">
         <v>净卖: -3194.79万</v>
       </c>
       <c r="E26">
@@ -11813,40 +11813,40 @@
       <c r="H26">
         <v>-2.87</v>
       </c>
-      <c r="I26" s="319">
+      <c r="I26" s="312">
         <v>-7.31</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="316">
         <v>-11.37</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="317">
         <v>-8.41</v>
       </c>
-      <c r="L26" s="311">
+      <c r="L26" s="313">
         <v>-9.37</v>
       </c>
-      <c r="M26" s="312">
+      <c r="M26" s="321">
         <v>-6.42</v>
       </c>
-      <c r="N26" s="313">
+      <c r="N26" s="314">
         <v>-9.67</v>
       </c>
-      <c r="O26" s="314">
+      <c r="O26" s="318">
         <v>-7.38</v>
       </c>
-      <c r="P26" s="315">
+      <c r="P26" s="322">
         <v>-6.64</v>
       </c>
-      <c r="Q26" s="316">
+      <c r="Q26" s="319">
         <v>-2.88</v>
       </c>
       <c r="R26" s="320">
         <v>-1.4</v>
       </c>
-      <c r="S26" s="321">
+      <c r="S26" s="323">
         <v>5.61</v>
       </c>
-      <c r="T26" s="317">
+      <c r="T26" s="311">
         <v>-9.37</v>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       <c r="C27" t="str">
         <v>002591</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="335" t="str">
         <v>净买: 2640.64万</v>
       </c>
       <c r="E27">
@@ -11875,40 +11875,40 @@
       <c r="H27">
         <v>1.86</v>
       </c>
-      <c r="I27" s="324">
+      <c r="I27" s="336">
         <v>3.65</v>
       </c>
-      <c r="J27" s="334">
+      <c r="J27" s="328">
         <v>3.04</v>
       </c>
-      <c r="K27" s="325">
+      <c r="K27" s="331">
         <v>13.37</v>
       </c>
-      <c r="L27" s="326">
+      <c r="L27" s="324">
         <v>24.77</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="329">
         <v>12.31</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="332">
         <v>10.49</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="326">
         <v>7.6</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="325">
         <v>3.8</v>
       </c>
-      <c r="Q27" s="331">
+      <c r="Q27" s="333">
         <v>6.23</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="327">
         <v>10.33</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="330">
         <v>15.35</v>
       </c>
-      <c r="T27" s="335">
+      <c r="T27" s="334">
         <v>4.26</v>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       <c r="C28" t="str">
         <v>002591</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="339" t="str">
         <v>净卖: -2864.29万</v>
       </c>
       <c r="E28">
@@ -11937,40 +11937,40 @@
       <c r="H28">
         <v>10.05</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="343">
         <v>0</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="340">
         <v>-9.99</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="337">
         <v>-11.45</v>
       </c>
-      <c r="L28" s="339">
+      <c r="L28" s="348">
         <v>-13.76</v>
       </c>
-      <c r="M28" s="340">
+      <c r="M28" s="344">
         <v>-16.81</v>
       </c>
-      <c r="N28" s="342">
+      <c r="N28" s="349">
         <v>-14.86</v>
       </c>
-      <c r="O28" s="343">
+      <c r="O28" s="341">
         <v>-11.57</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="342">
         <v>-7.55</v>
       </c>
-      <c r="Q28" s="337">
+      <c r="Q28" s="345">
         <v>-10.6</v>
       </c>
-      <c r="R28" s="338">
+      <c r="R28" s="346">
         <v>-12.79</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="347">
         <v>-12.18</v>
       </c>
-      <c r="T28" s="346">
+      <c r="T28" s="338">
         <v>-16.44</v>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       <c r="C29" t="str">
         <v>920834</v>
       </c>
-      <c r="D29" s="353" t="str">
+      <c r="D29" s="357" t="str">
         <v>净买: 444.90万</v>
       </c>
       <c r="E29">
@@ -11999,40 +11999,40 @@
       <c r="H29">
         <v>0.05</v>
       </c>
-      <c r="I29" s="362">
+      <c r="I29" s="356">
         <v>4.65</v>
       </c>
-      <c r="J29" s="354">
+      <c r="J29" s="350">
         <v>8.98</v>
       </c>
-      <c r="K29" s="351">
+      <c r="K29" s="360">
         <v>-2.49</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="358">
         <v>-6.06</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="351">
         <v>-1.24</v>
       </c>
       <c r="N29" s="361">
         <v>-3.08</v>
       </c>
-      <c r="O29" s="352">
+      <c r="O29" s="362">
         <v>-8.49</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="359">
         <v>-8.22</v>
       </c>
-      <c r="Q29" s="350">
+      <c r="Q29" s="352">
         <v>-9.84</v>
       </c>
-      <c r="R29" s="357">
+      <c r="R29" s="353">
         <v>-1.03</v>
       </c>
-      <c r="S29" s="358">
+      <c r="S29" s="354">
         <v>-3.62</v>
       </c>
-      <c r="T29" s="359">
+      <c r="T29" s="355">
         <v>-33.8</v>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
       <c r="C30" t="str">
         <v>000592</v>
       </c>
-      <c r="D30" s="364" t="str">
+      <c r="D30" s="365" t="str">
         <v>净卖: -3288.03万</v>
       </c>
       <c r="E30">
@@ -12064,13 +12064,13 @@
       <c r="I30" s="374">
         <v>9.02</v>
       </c>
-      <c r="J30" s="365">
+      <c r="J30" s="372">
         <v>19.94</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="369">
         <v>7.92</v>
       </c>
-      <c r="L30" s="375">
+      <c r="L30" s="366">
         <v>-2.91</v>
       </c>
       <c r="M30" s="370">
@@ -12079,22 +12079,22 @@
       <c r="N30" s="371">
         <v>-6.41</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="373">
         <v>-2.3</v>
       </c>
       <c r="P30" s="367">
         <v>7.52</v>
       </c>
-      <c r="Q30" s="363">
+      <c r="Q30" s="368">
         <v>13.93</v>
       </c>
-      <c r="R30" s="368">
+      <c r="R30" s="375">
         <v>25.35</v>
       </c>
-      <c r="S30" s="373">
+      <c r="S30" s="363">
         <v>12.93</v>
       </c>
-      <c r="T30" s="369">
+      <c r="T30" s="364">
         <v>9.62</v>
       </c>
     </row>
@@ -12108,7 +12108,7 @@
       <c r="C31" t="str">
         <v>688227</v>
       </c>
-      <c r="D31" s="382" t="str">
+      <c r="D31" s="381" t="str">
         <v>净卖: -490.20万</v>
       </c>
       <c r="E31">
@@ -12123,40 +12123,40 @@
       <c r="H31">
         <v>20</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="376">
         <v>0</v>
       </c>
       <c r="J31" s="384">
         <v>19.99</v>
       </c>
-      <c r="K31" s="385">
+      <c r="K31" s="386">
         <v>43.98</v>
       </c>
-      <c r="L31" s="376">
+      <c r="L31" s="382">
         <v>71.32</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="387">
         <v>67.14</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="377">
         <v>66.93</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="388">
         <v>64.79</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="378">
         <v>48.94</v>
       </c>
-      <c r="Q31" s="388">
+      <c r="Q31" s="385">
         <v>50.96</v>
       </c>
-      <c r="R31" s="377">
+      <c r="R31" s="383">
         <v>40.37</v>
       </c>
-      <c r="S31" s="380">
+      <c r="S31" s="379">
         <v>43</v>
       </c>
-      <c r="T31" s="381">
+      <c r="T31" s="380">
         <v>106.77</v>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       <c r="C32" t="str">
         <v>002565</v>
       </c>
-      <c r="D32" s="400" t="str">
+      <c r="D32" s="401" t="str">
         <v>净卖: -2942.55万</v>
       </c>
       <c r="E32">
@@ -12185,40 +12185,40 @@
       <c r="H32">
         <v>-0.67</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="389">
         <v>-0.4</v>
       </c>
-      <c r="J32" s="390">
+      <c r="J32" s="394">
         <v>-1.75</v>
       </c>
-      <c r="K32" s="398">
+      <c r="K32" s="392">
         <v>8.08</v>
       </c>
-      <c r="L32" s="394">
+      <c r="L32" s="395">
         <v>18.84</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="390">
         <v>30.69</v>
       </c>
-      <c r="N32" s="392">
+      <c r="N32" s="396">
         <v>43.74</v>
       </c>
-      <c r="O32" s="395">
+      <c r="O32" s="397">
         <v>45.63</v>
       </c>
-      <c r="P32" s="401">
+      <c r="P32" s="398">
         <v>60.16</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="393">
         <v>76.18</v>
       </c>
-      <c r="R32" s="396">
+      <c r="R32" s="391">
         <v>77.66</v>
       </c>
-      <c r="S32" s="389">
+      <c r="S32" s="399">
         <v>81.29</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="400">
         <v>154.64</v>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       <c r="C33" t="str">
         <v>920826</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="412" t="str">
         <v>净买: 408.58万</v>
       </c>
       <c r="E33">
@@ -12247,40 +12247,40 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" s="411">
+      <c r="I33" s="402">
         <v>3.25</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="409">
         <v>-3.4</v>
       </c>
-      <c r="K33" s="406">
+      <c r="K33" s="404">
         <v>-2.17</v>
       </c>
-      <c r="L33" s="408">
+      <c r="L33" s="405">
         <v>-0.65</v>
       </c>
-      <c r="M33" s="403">
+      <c r="M33" s="406">
         <v>-2.46</v>
       </c>
-      <c r="N33" s="404">
+      <c r="N33" s="410">
         <v>-2.6</v>
       </c>
-      <c r="O33" s="409">
+      <c r="O33" s="407">
         <v>-0.94</v>
       </c>
-      <c r="P33" s="407">
+      <c r="P33" s="413">
         <v>-1.37</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="403">
         <v>0.58</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="408">
         <v>4.63</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="411">
         <v>3.54</v>
       </c>
-      <c r="T33" s="402">
+      <c r="T33" s="414">
         <v>-21.26</v>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       <c r="C34" t="str">
         <v>603122</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="426" t="str">
         <v>净卖: -1862.43万</v>
       </c>
       <c r="E34">
@@ -12309,40 +12309,40 @@
       <c r="H34">
         <v>-6.1</v>
       </c>
-      <c r="I34" s="415">
+      <c r="I34" s="420">
         <v>-4.17</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="422">
         <v>0.5</v>
       </c>
-      <c r="K34" s="416">
+      <c r="K34" s="423">
         <v>10.54</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="421">
         <v>21.58</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="417">
         <v>13.25</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="427">
         <v>16.25</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="424">
         <v>9.79</v>
       </c>
       <c r="P34" s="418">
         <v>5.25</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="425">
         <v>11.67</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="415">
         <v>9.17</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="416">
         <v>14.38</v>
       </c>
-      <c r="T34" s="424">
+      <c r="T34" s="419">
         <v>-32.67</v>
       </c>
     </row>
@@ -12371,40 +12371,40 @@
       <c r="H35">
         <v>6.26</v>
       </c>
-      <c r="I35" s="431">
+      <c r="I35" s="437">
         <v>5.9</v>
       </c>
       <c r="J35" s="435">
         <v>2.61</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="431">
         <v>3.96</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="428">
         <v>-1.42</v>
       </c>
-      <c r="M35" s="432">
+      <c r="M35" s="436">
         <v>-2.72</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="432">
         <v>-3.17</v>
       </c>
-      <c r="O35" s="439">
+      <c r="O35" s="438">
         <v>-2.57</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="433">
         <v>-2.24</v>
       </c>
-      <c r="Q35" s="428">
+      <c r="Q35" s="439">
         <v>0.3</v>
       </c>
-      <c r="R35" s="436">
+      <c r="R35" s="434">
         <v>1.04</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="429">
         <v>1.08</v>
       </c>
-      <c r="T35" s="429">
+      <c r="T35" s="440">
         <v>-15.75</v>
       </c>
     </row>
@@ -12418,7 +12418,7 @@
       <c r="C36" t="str">
         <v>601616</v>
       </c>
-      <c r="D36" s="443" t="str">
+      <c r="D36" s="442" t="str">
         <v>净卖: -1517.47万</v>
       </c>
       <c r="E36">
@@ -12433,40 +12433,40 @@
       <c r="H36">
         <v>4.8</v>
       </c>
-      <c r="I36" s="451">
+      <c r="I36" s="450">
         <v>5</v>
       </c>
-      <c r="J36" s="444">
+      <c r="J36" s="453">
         <v>15.42</v>
       </c>
-      <c r="K36" s="452">
+      <c r="K36" s="446">
         <v>26.88</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="443">
         <v>21.25</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="444">
         <v>21.25</v>
       </c>
-      <c r="N36" s="441">
+      <c r="N36" s="447">
         <v>11.04</v>
       </c>
-      <c r="O36" s="449">
+      <c r="O36" s="445">
         <v>8.33</v>
       </c>
-      <c r="P36" s="446">
+      <c r="P36" s="451">
         <v>7.08</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="448">
         <v>3.33</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="452">
         <v>2.08</v>
       </c>
-      <c r="S36" s="448">
+      <c r="S36" s="449">
         <v>12.29</v>
       </c>
-      <c r="T36" s="442">
+      <c r="T36" s="441">
         <v>0.21</v>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       <c r="C37" t="str">
         <v>920471</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="466" t="str">
         <v>净卖: -990.93万</v>
       </c>
       <c r="E37">
@@ -12495,40 +12495,40 @@
       <c r="H37">
         <v>0.37</v>
       </c>
-      <c r="I37" s="455">
+      <c r="I37" s="454">
         <v>29.46</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="455">
         <v>33.16</v>
       </c>
-      <c r="K37" s="460">
+      <c r="K37" s="463">
         <v>26.05</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="460">
         <v>32.79</v>
       </c>
-      <c r="M37" s="456">
+      <c r="M37" s="464">
         <v>40.78</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="465">
         <v>27.02</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="456">
         <v>35.83</v>
       </c>
-      <c r="P37" s="465">
+      <c r="P37" s="459">
         <v>53.07</v>
       </c>
-      <c r="Q37" s="466">
+      <c r="Q37" s="461">
         <v>57.29</v>
       </c>
-      <c r="R37" s="457">
+      <c r="R37" s="462">
         <v>37.45</v>
       </c>
-      <c r="S37" s="458">
+      <c r="S37" s="457">
         <v>44.26</v>
       </c>
-      <c r="T37" s="454">
+      <c r="T37" s="458">
         <v>-4.81</v>
       </c>
     </row>
@@ -12542,7 +12542,7 @@
       <c r="C38" t="str">
         <v>300986</v>
       </c>
-      <c r="D38" s="476" t="str">
+      <c r="D38" s="473" t="str">
         <v>净卖: -1994.11万</v>
       </c>
       <c r="E38">
@@ -12557,40 +12557,40 @@
       <c r="H38">
         <v>5.63</v>
       </c>
-      <c r="I38" s="471">
+      <c r="I38" s="474">
         <v>12.67</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="477">
         <v>16</v>
       </c>
-      <c r="K38" s="477">
+      <c r="K38" s="467">
         <v>10.67</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="468">
         <v>32.8</v>
       </c>
-      <c r="M38" s="467">
+      <c r="M38" s="469">
         <v>36.67</v>
       </c>
-      <c r="N38" s="475">
+      <c r="N38" s="470">
         <v>44.23</v>
       </c>
-      <c r="O38" s="468">
+      <c r="O38" s="475">
         <v>25.5</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="471">
         <v>30.87</v>
       </c>
-      <c r="Q38" s="469">
+      <c r="Q38" s="472">
         <v>24.5</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="478">
         <v>26</v>
       </c>
-      <c r="S38" s="470">
+      <c r="S38" s="476">
         <v>41</v>
       </c>
-      <c r="T38" s="473">
+      <c r="T38" s="479">
         <v>-17.47</v>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
       <c r="C39" t="str">
         <v>920414</v>
       </c>
-      <c r="D39" s="485" t="str">
+      <c r="D39" s="484" t="str">
         <v>净卖: -1486.22万</v>
       </c>
       <c r="E39">
@@ -12619,40 +12619,40 @@
       <c r="H39">
         <v>0.68</v>
       </c>
-      <c r="I39" s="490">
+      <c r="I39" s="481">
         <v>29.11</v>
       </c>
-      <c r="J39" s="487">
+      <c r="J39" s="488">
         <v>33.83</v>
       </c>
-      <c r="K39" s="491">
+      <c r="K39" s="482">
         <v>44.34</v>
       </c>
-      <c r="L39" s="492">
+      <c r="L39" s="485">
         <v>28.73</v>
       </c>
-      <c r="M39" s="488">
+      <c r="M39" s="483">
         <v>21.38</v>
       </c>
-      <c r="N39" s="480">
+      <c r="N39" s="489">
         <v>13.28</v>
       </c>
-      <c r="O39" s="486">
+      <c r="O39" s="490">
         <v>14.93</v>
       </c>
-      <c r="P39" s="489">
+      <c r="P39" s="486">
         <v>28.43</v>
       </c>
-      <c r="Q39" s="482">
+      <c r="Q39" s="491">
         <v>45.16</v>
       </c>
-      <c r="R39" s="483">
+      <c r="R39" s="492">
         <v>27.01</v>
       </c>
-      <c r="S39" s="481">
+      <c r="S39" s="480">
         <v>29.63</v>
       </c>
-      <c r="T39" s="484">
+      <c r="T39" s="487">
         <v>-2.25</v>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       <c r="C40" t="str">
         <v>920414</v>
       </c>
-      <c r="D40" s="501" t="str">
+      <c r="D40" s="495" t="str">
         <v>净卖: -1162.25万</v>
       </c>
       <c r="E40">
@@ -12681,40 +12681,40 @@
       <c r="H40">
         <v>-9.19</v>
       </c>
-      <c r="I40" s="498">
+      <c r="I40" s="501">
         <v>18.77</v>
       </c>
-      <c r="J40" s="504">
+      <c r="J40" s="505">
         <v>5.93</v>
       </c>
-      <c r="K40" s="505">
+      <c r="K40" s="502">
         <v>-0.12</v>
       </c>
-      <c r="L40" s="495">
+      <c r="L40" s="500">
         <v>-6.79</v>
       </c>
-      <c r="M40" s="493">
+      <c r="M40" s="496">
         <v>-5.43</v>
       </c>
-      <c r="N40" s="502">
+      <c r="N40" s="497">
         <v>5.68</v>
       </c>
-      <c r="O40" s="494">
+      <c r="O40" s="503">
         <v>19.44</v>
       </c>
-      <c r="P40" s="496">
+      <c r="P40" s="498">
         <v>4.51</v>
       </c>
-      <c r="Q40" s="499">
+      <c r="Q40" s="493">
         <v>6.67</v>
       </c>
-      <c r="R40" s="500">
+      <c r="R40" s="504">
         <v>9.26</v>
       </c>
-      <c r="S40" s="503">
+      <c r="S40" s="499">
         <v>8.09</v>
       </c>
-      <c r="T40" s="497">
+      <c r="T40" s="494">
         <v>-19.57</v>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       <c r="C41" t="str">
         <v>920414</v>
       </c>
-      <c r="D41" s="514" t="str">
+      <c r="D41" s="516" t="str">
         <v>净卖: -333.39万</v>
       </c>
       <c r="E41">
@@ -12743,25 +12743,25 @@
       <c r="H41">
         <v>-6.81</v>
       </c>
-      <c r="I41" s="509">
+      <c r="I41" s="508">
         <v>-4.29</v>
       </c>
-      <c r="J41" s="512">
+      <c r="J41" s="509">
         <v>-9.76</v>
       </c>
-      <c r="K41" s="513">
+      <c r="K41" s="511">
         <v>-15.78</v>
       </c>
-      <c r="L41" s="515">
+      <c r="L41" s="517">
         <v>-14.56</v>
       </c>
-      <c r="M41" s="510">
+      <c r="M41" s="512">
         <v>-4.52</v>
       </c>
-      <c r="N41" s="511">
+      <c r="N41" s="513">
         <v>7.92</v>
       </c>
-      <c r="O41" s="517">
+      <c r="O41" s="510">
         <v>-5.58</v>
       </c>
       <c r="P41" s="518">
@@ -12770,13 +12770,13 @@
       <c r="Q41" s="506">
         <v>-1.28</v>
       </c>
-      <c r="R41" s="507">
+      <c r="R41" s="514">
         <v>-2.34</v>
       </c>
-      <c r="S41" s="508">
+      <c r="S41" s="515">
         <v>-8.25</v>
       </c>
-      <c r="T41" s="516">
+      <c r="T41" s="507">
         <v>-27.33</v>
       </c>
     </row>
@@ -12790,7 +12790,7 @@
       <c r="C42" t="str">
         <v>001376</v>
       </c>
-      <c r="D42" s="525" t="str">
+      <c r="D42" s="524" t="str">
         <v>净卖: -998.65万</v>
       </c>
       <c r="E42">
@@ -12805,40 +12805,40 @@
       <c r="H42">
         <v>4.53</v>
       </c>
-      <c r="I42" s="526">
+      <c r="I42" s="529">
         <v>5.24</v>
       </c>
-      <c r="J42" s="522">
+      <c r="J42" s="525">
         <v>1.85</v>
       </c>
-      <c r="K42" s="523">
+      <c r="K42" s="530">
         <v>-5.24</v>
       </c>
-      <c r="L42" s="529">
+      <c r="L42" s="526">
         <v>-8.63</v>
       </c>
-      <c r="M42" s="524">
+      <c r="M42" s="527">
         <v>-11.16</v>
       </c>
-      <c r="N42" s="527">
+      <c r="N42" s="531">
         <v>-15.62</v>
       </c>
-      <c r="O42" s="528">
+      <c r="O42" s="521">
         <v>-14.59</v>
       </c>
-      <c r="P42" s="531">
+      <c r="P42" s="528">
         <v>-14.81</v>
       </c>
       <c r="Q42" s="519">
         <v>-17.55</v>
       </c>
-      <c r="R42" s="530">
+      <c r="R42" s="520">
         <v>-9.31</v>
       </c>
-      <c r="S42" s="520">
+      <c r="S42" s="522">
         <v>-12.45</v>
       </c>
-      <c r="T42" s="521">
+      <c r="T42" s="523">
         <v>-30.99</v>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       <c r="C43" t="str">
         <v>601015</v>
       </c>
-      <c r="D43" s="539" t="str">
+      <c r="D43" s="534" t="str">
         <v>净卖: -813.51万</v>
       </c>
       <c r="E43">
@@ -12867,40 +12867,40 @@
       <c r="H43">
         <v>-5.9</v>
       </c>
-      <c r="I43" s="534">
+      <c r="I43" s="540">
         <v>-4.41</v>
       </c>
-      <c r="J43" s="540">
+      <c r="J43" s="533">
         <v>-2.55</v>
       </c>
-      <c r="K43" s="535">
+      <c r="K43" s="537">
         <v>7.19</v>
       </c>
-      <c r="L43" s="536">
+      <c r="L43" s="538">
         <v>17.87</v>
       </c>
-      <c r="M43" s="537">
+      <c r="M43" s="541">
         <v>19.95</v>
       </c>
-      <c r="N43" s="544">
+      <c r="N43" s="535">
         <v>18.33</v>
       </c>
-      <c r="O43" s="532">
+      <c r="O43" s="542">
         <v>13.69</v>
       </c>
-      <c r="P43" s="542">
+      <c r="P43" s="543">
         <v>11.6</v>
       </c>
-      <c r="Q43" s="538">
+      <c r="Q43" s="536">
         <v>5.57</v>
       </c>
-      <c r="R43" s="543">
+      <c r="R43" s="544">
         <v>3.25</v>
       </c>
-      <c r="S43" s="533">
+      <c r="S43" s="539">
         <v>13.69</v>
       </c>
-      <c r="T43" s="541">
+      <c r="T43" s="532">
         <v>-9.98</v>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       <c r="C44" t="str">
         <v>920299</v>
       </c>
-      <c r="D44" s="545" t="str">
+      <c r="D44" s="552" t="str">
         <v>净卖: -590.29万</v>
       </c>
       <c r="E44">
@@ -12932,37 +12932,37 @@
       <c r="I44" s="551">
         <v>10.93</v>
       </c>
-      <c r="J44" s="546">
+      <c r="J44" s="553">
         <v>7.07</v>
       </c>
-      <c r="K44" s="552">
+      <c r="K44" s="547">
         <v>4.57</v>
       </c>
-      <c r="L44" s="547">
+      <c r="L44" s="548">
         <v>8.44</v>
       </c>
-      <c r="M44" s="553">
+      <c r="M44" s="554">
         <v>4.89</v>
       </c>
-      <c r="N44" s="554">
+      <c r="N44" s="555">
         <v>1.09</v>
       </c>
-      <c r="O44" s="555">
+      <c r="O44" s="557">
         <v>-1.2</v>
       </c>
       <c r="P44" s="549">
         <v>-0.42</v>
       </c>
-      <c r="Q44" s="548">
+      <c r="Q44" s="556">
         <v>-2.85</v>
       </c>
-      <c r="R44" s="556">
+      <c r="R44" s="550">
         <v>-4.75</v>
       </c>
-      <c r="S44" s="557">
+      <c r="S44" s="545">
         <v>-4.08</v>
       </c>
-      <c r="T44" s="550">
+      <c r="T44" s="546">
         <v>-12.44</v>
       </c>
     </row>
@@ -12976,7 +12976,7 @@
       <c r="C45" t="str">
         <v>688079</v>
       </c>
-      <c r="D45" s="558" t="str">
+      <c r="D45" s="562" t="str">
         <v>净卖: -1226.18万</v>
       </c>
       <c r="E45">
@@ -12991,40 +12991,40 @@
       <c r="H45">
         <v>4.51</v>
       </c>
-      <c r="I45" s="570">
+      <c r="I45" s="566">
         <v>14.78</v>
       </c>
-      <c r="J45" s="565">
+      <c r="J45" s="567">
         <v>9.3</v>
       </c>
-      <c r="K45" s="561">
+      <c r="K45" s="568">
         <v>11.46</v>
       </c>
-      <c r="L45" s="559">
+      <c r="L45" s="563">
         <v>13.87</v>
       </c>
-      <c r="M45" s="566">
+      <c r="M45" s="558">
         <v>15.37</v>
       </c>
-      <c r="N45" s="560">
+      <c r="N45" s="559">
         <v>18.69</v>
       </c>
-      <c r="O45" s="567">
+      <c r="O45" s="564">
         <v>12.96</v>
       </c>
-      <c r="P45" s="562">
+      <c r="P45" s="569">
         <v>11.3</v>
       </c>
-      <c r="Q45" s="568">
+      <c r="Q45" s="570">
         <v>5.81</v>
       </c>
-      <c r="R45" s="563">
+      <c r="R45" s="561">
         <v>8.72</v>
       </c>
-      <c r="S45" s="564">
+      <c r="S45" s="560">
         <v>4.57</v>
       </c>
-      <c r="T45" s="569">
+      <c r="T45" s="565">
         <v>34.97</v>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
       <c r="C46" t="str">
         <v>301361</v>
       </c>
-      <c r="D46" s="573" t="str">
+      <c r="D46" s="580" t="str">
         <v>净买: 1425.27万</v>
       </c>
       <c r="E46">
@@ -13053,40 +13053,40 @@
       <c r="H46">
         <v>0.99</v>
       </c>
-      <c r="I46" s="578">
+      <c r="I46" s="577">
         <v>13.48</v>
       </c>
-      <c r="J46" s="579">
+      <c r="J46" s="575">
         <v>9.11</v>
       </c>
-      <c r="K46" s="580">
+      <c r="K46" s="573">
         <v>-1.68</v>
       </c>
-      <c r="L46" s="583">
+      <c r="L46" s="576">
         <v>2.25</v>
       </c>
-      <c r="M46" s="571">
+      <c r="M46" s="578">
         <v>-5.86</v>
       </c>
-      <c r="N46" s="572">
+      <c r="N46" s="581">
         <v>-3.8</v>
       </c>
-      <c r="O46" s="576">
+      <c r="O46" s="582">
         <v>-7.84</v>
       </c>
-      <c r="P46" s="577">
+      <c r="P46" s="583">
         <v>-9.84</v>
       </c>
-      <c r="Q46" s="581">
+      <c r="Q46" s="574">
         <v>-14.77</v>
       </c>
-      <c r="R46" s="582">
+      <c r="R46" s="579">
         <v>-9.43</v>
       </c>
-      <c r="S46" s="574">
+      <c r="S46" s="571">
         <v>-9.64</v>
       </c>
-      <c r="T46" s="575">
+      <c r="T46" s="572">
         <v>-12.39</v>
       </c>
     </row>
@@ -13100,7 +13100,7 @@
       <c r="C47" t="str">
         <v>688485</v>
       </c>
-      <c r="D47" s="586" t="str">
+      <c r="D47" s="584" t="str">
         <v>净买: 1305.22万</v>
       </c>
       <c r="E47">
@@ -13115,40 +13115,40 @@
       <c r="H47">
         <v>-6.79</v>
       </c>
-      <c r="I47" s="595">
+      <c r="I47" s="594">
         <v>0.15</v>
       </c>
-      <c r="J47" s="587">
+      <c r="J47" s="585">
         <v>-7.77</v>
       </c>
-      <c r="K47" s="590">
+      <c r="K47" s="589">
         <v>-7.32</v>
       </c>
-      <c r="L47" s="588">
+      <c r="L47" s="590">
         <v>-2.61</v>
       </c>
-      <c r="M47" s="596">
+      <c r="M47" s="595">
         <v>16.88</v>
       </c>
       <c r="N47" s="591">
         <v>25.13</v>
       </c>
-      <c r="O47" s="592">
+      <c r="O47" s="586">
         <v>50.15</v>
       </c>
-      <c r="P47" s="593">
+      <c r="P47" s="592">
         <v>48.24</v>
       </c>
-      <c r="Q47" s="594">
+      <c r="Q47" s="587">
         <v>51.23</v>
       </c>
-      <c r="R47" s="584">
+      <c r="R47" s="593">
         <v>65.42</v>
       </c>
-      <c r="S47" s="589">
+      <c r="S47" s="588">
         <v>59.86</v>
       </c>
-      <c r="T47" s="585">
+      <c r="T47" s="596">
         <v>62.43</v>
       </c>
     </row>
@@ -13211,40 +13211,40 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="606">
+      <c r="I49" s="600">
         <v>78.26</v>
       </c>
-      <c r="J49" s="607">
+      <c r="J49" s="602">
         <v>80.43</v>
       </c>
-      <c r="K49" s="599">
+      <c r="K49" s="605">
         <v>76.09</v>
       </c>
-      <c r="L49" s="608">
+      <c r="L49" s="606">
         <v>71.74</v>
       </c>
-      <c r="M49" s="597">
+      <c r="M49" s="598">
         <v>69.57</v>
       </c>
-      <c r="N49" s="601">
+      <c r="N49" s="603">
         <v>69.57</v>
       </c>
-      <c r="O49" s="598">
+      <c r="O49" s="607">
         <v>63.04</v>
       </c>
-      <c r="P49" s="602">
+      <c r="P49" s="599">
         <v>69.57</v>
       </c>
-      <c r="Q49" s="603">
+      <c r="Q49" s="601">
         <v>71.74</v>
       </c>
       <c r="R49" s="604">
         <v>75.56</v>
       </c>
-      <c r="S49" s="605">
+      <c r="S49" s="608">
         <v>80</v>
       </c>
-      <c r="T49" s="600">
+      <c r="T49" s="597">
         <v>43.48</v>
       </c>
     </row>
@@ -13259,40 +13259,40 @@
       <c r="F50" t="str"/>
       <c r="G50" t="str"/>
       <c r="H50" t="str"/>
-      <c r="I50" s="617">
+      <c r="I50" s="610">
         <v>8.72</v>
       </c>
-      <c r="J50" s="613">
+      <c r="J50" s="611">
         <v>8.72</v>
       </c>
-      <c r="K50" s="614">
+      <c r="K50" s="618">
         <v>8.24</v>
       </c>
-      <c r="L50" s="618">
+      <c r="L50" s="619">
         <v>10.18</v>
       </c>
-      <c r="M50" s="620">
+      <c r="M50" s="617">
         <v>11.36</v>
       </c>
-      <c r="N50" s="610">
+      <c r="N50" s="613">
         <v>10.81</v>
       </c>
-      <c r="O50" s="611">
+      <c r="O50" s="614">
         <v>11.29</v>
       </c>
       <c r="P50" s="615">
         <v>11.98</v>
       </c>
-      <c r="Q50" s="616">
+      <c r="Q50" s="612">
         <v>12.74</v>
       </c>
-      <c r="R50" s="619">
+      <c r="R50" s="620">
         <v>14.57</v>
       </c>
-      <c r="S50" s="612">
+      <c r="S50" s="609">
         <v>16.24</v>
       </c>
-      <c r="T50" s="609">
+      <c r="T50" s="616">
         <v>12.06</v>
       </c>
     </row>
